--- a/Catàleg exercicis.xlsx
+++ b/Catàleg exercicis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="574">
   <si>
     <t>ID</t>
   </si>
@@ -78,6 +78,9 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Link</t>
+  </si>
+  <si>
     <t>ex_elliptical</t>
   </si>
   <si>
@@ -114,6 +117,9 @@
     <t>cardio; baix impacte</t>
   </si>
   <si>
+    <t>Pedala a ritme suau i estable, amb el tronc dret i els peus ben recolzats. Augmenta progressivament la intensitat sense perdre fluïdesa.</t>
+  </si>
+  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -150,6 +156,9 @@
     <t>mobilitat; seqüència</t>
   </si>
   <si>
+    <t>Fes una seqüència controlada de mobilitat de turmell, maluc i columna toràcica, recorrent rangs còmodes i evitant rebots.</t>
+  </si>
+  <si>
     <t>Seqüència combinada registrada als entrenaments</t>
   </si>
   <si>
@@ -183,6 +192,9 @@
     <t>activació; banda</t>
   </si>
   <si>
+    <t>Col·loca la banda al voltant de les cames, flexiona lleument genolls i malucs i fes passos laterals mantenint tensió constant a la banda.</t>
+  </si>
+  <si>
     <t>ex_band_pull_apart</t>
   </si>
   <si>
@@ -210,6 +222,9 @@
     <t>activació escapular</t>
   </si>
   <si>
+    <t>Subjecta la banda davant del pit amb els braços gairebé estesos i obre-la portant les mans cap als costats mentre apropes les escàpules.</t>
+  </si>
+  <si>
     <t>ex_isometric_glute_bridge</t>
   </si>
   <si>
@@ -243,6 +258,9 @@
     <t>activació glutis; isomètric</t>
   </si>
   <si>
+    <t>Estira’t boca amunt amb genolls flexionats, eleva la pelvis contraient els glutis i mantén la posició sense arquejar la zona lumbar.</t>
+  </si>
+  <si>
     <t>ex_vertical_jump</t>
   </si>
   <si>
@@ -264,6 +282,9 @@
     <t>pliometria; explosiu</t>
   </si>
   <si>
+    <t>Flexiona malucs i genolls, impulsa’t verticalment amb els braços i aterra suaument amb genolls alineats i control de la posició.</t>
+  </si>
+  <si>
     <t>ex_lateral_jump</t>
   </si>
   <si>
@@ -282,6 +303,9 @@
     <t>pliometria; lateral</t>
   </si>
   <si>
+    <t>Desplaça’t amb un salt cap al costat i aterra amb control, absorbint l’impacte amb maluc, genoll i turmell alineats.</t>
+  </si>
+  <si>
     <t>ex_semisumo_deadlift</t>
   </si>
   <si>
@@ -315,6 +339,9 @@
     <t>compost; cadena posterior</t>
   </si>
   <si>
+    <t>Col·loca els peus una mica més oberts que les espatlles, agafa la barra i eleva-la estenent malucs i genolls amb l’esquena neutra.</t>
+  </si>
+  <si>
     <t>ex_pull_up</t>
   </si>
   <si>
@@ -345,6 +372,9 @@
     <t>pes corporal; tracció</t>
   </si>
   <si>
+    <t>Penja’t de la barra, activa escàpules i abdomen i puja el pit cap a la barra sense balancejar-te; baixa de manera controlada.</t>
+  </si>
+  <si>
     <t>ex_incline_db_press</t>
   </si>
   <si>
@@ -372,6 +402,9 @@
     <t>empenta; manuelles</t>
   </si>
   <si>
+    <t>Recolza’t en un banc inclinat, baixa les manuelles de forma controlada cap al pit i empeny-les amunt mantenint les escàpules estables.</t>
+  </si>
+  <si>
     <t>ex_barbell_row</t>
   </si>
   <si>
@@ -396,6 +429,9 @@
     <t>tracció; barra</t>
   </si>
   <si>
+    <t>Amb el tronc inclinat i l’esquena neutra, porta la barra cap a l’abdomen amb els colzes enrere i baixa-la de manera controlada.</t>
+  </si>
+  <si>
     <t>ex_hip_thrust</t>
   </si>
   <si>
@@ -411,6 +447,9 @@
     <t>glutis; extensió maluc</t>
   </si>
   <si>
+    <t>Recolza la part alta de l’esquena al banc, empeny la pelvis cap amunt contraient glutis i acaba amb malucs estesos sense hiperextensió lumbar.</t>
+  </si>
+  <si>
     <t>ex_cable_pullover</t>
   </si>
   <si>
@@ -438,6 +477,9 @@
     <t>dorsal; politja</t>
   </si>
   <si>
+    <t>Davant d’una politja alta, mantén els braços gairebé estesos i porta la barra o corda cap a les cuixes movent sobretot les espatlles.</t>
+  </si>
+  <si>
     <t>ex_db_pullover</t>
   </si>
   <si>
@@ -456,6 +498,9 @@
     <t>pullover</t>
   </si>
   <si>
+    <t>Estirat en un banc, sostén una manuella sobre el pit i porta-la lentament darrere del cap mantenint els colzes lleument flexionats; torna controlant.</t>
+  </si>
+  <si>
     <t>ex_push_up</t>
   </si>
   <si>
@@ -480,6 +525,9 @@
     <t>pes corporal</t>
   </si>
   <si>
+    <t>En posició de planxa, baixa el cos mantenint-lo alineat fins apropar el pit a terra i empeny fins estendre els braços.</t>
+  </si>
+  <si>
     <t>ex_farmer_walk</t>
   </si>
   <si>
@@ -510,6 +558,9 @@
     <t>carry; grip</t>
   </si>
   <si>
+    <t>Camina dret amb una càrrega a cada mà, braços llargs i tronc estable, evitant inclinar-te o deixar caure les espatlles.</t>
+  </si>
+  <si>
     <t>ex_plank_plate_drag</t>
   </si>
   <si>
@@ -540,6 +591,9 @@
     <t>core; antirotació</t>
   </si>
   <si>
+    <t>En planxa alta, arrossega el disc d’un costat a l’altre amb una mà intentant que pelvis i tronc girin el mínim possible.</t>
+  </si>
+  <si>
     <t>ex_copenhagen_plank</t>
   </si>
   <si>
@@ -573,6 +627,9 @@
     <t>core; adductors; isomètric</t>
   </si>
   <si>
+    <t>En planxa lateral, recolza la cama superior sobre un banc i eleva la pelvis mantenint el cos alineat; sostén la posició amb control.</t>
+  </si>
+  <si>
     <t>ex_bulgarian_split_squat</t>
   </si>
   <si>
@@ -597,6 +654,9 @@
     <t>unilateral; cames</t>
   </si>
   <si>
+    <t>Col·loca el peu del darrere sobre un banc, baixa verticalment flexionant la cama davantera i puja empenyent amb el peu de suport.</t>
+  </si>
+  <si>
     <t>ex_lat_pulldown</t>
   </si>
   <si>
@@ -621,6 +681,9 @@
     <t>tracció; politja</t>
   </si>
   <si>
+    <t>Assegut a la politja alta, porta la barra cap a la part alta del pit dirigint els colzes avall i enrere; torna sense perdre control escapular.</t>
+  </si>
+  <si>
     <t>ex_overhead_press</t>
   </si>
   <si>
@@ -648,6 +711,9 @@
     <t>empenta vertical</t>
   </si>
   <si>
+    <t>Des d’assegut o dempeus, empeny les manuelles o barra per sobre del cap mantenint abdomen actiu i evitant arquejar la zona lumbar.</t>
+  </si>
+  <si>
     <t>ex_trx_row</t>
   </si>
   <si>
@@ -669,6 +735,9 @@
     <t>suspensió; tracció</t>
   </si>
   <si>
+    <t>Agafa les nanses del TRX, mantén el cos alineat i apropa el pit a les mans portant els colzes enrere; torna controlant.</t>
+  </si>
+  <si>
     <t>ex_man_maker</t>
   </si>
   <si>
@@ -687,6 +756,9 @@
     <t>complex; cos sencer</t>
   </si>
   <si>
+    <t>Amb una manuella a cada mà, combina planxa, rem, incorporació i empenta per sobre del cap mantenint control del tronc durant tota la seqüència.</t>
+  </si>
+  <si>
     <t>ex_pallof_press</t>
   </si>
   <si>
@@ -705,6 +777,9 @@
     <t>Politja o banda elàstica</t>
   </si>
   <si>
+    <t>Col·loca’t de costat a una banda o politja, porta les mans davant del pit i estira els braços sense deixar que el tronc roti.</t>
+  </si>
+  <si>
     <t>ex_inverted_pushup</t>
   </si>
   <si>
@@ -726,6 +801,9 @@
     <t>Invertida/inclinada</t>
   </si>
   <si>
+    <t>Des d’una posició inclinada amb mans al terra, flexiona els colzes per apropar el cap o pit al terra i empeny per tornar amunt.</t>
+  </si>
+  <si>
     <t>Nom original poc específic</t>
   </si>
   <si>
@@ -753,6 +831,9 @@
     <t>core; isomètric</t>
   </si>
   <si>
+    <t>Seu amb cames esteses i mans darrere, eleva pelvis fins alinear tronc i cames i mantén espatlles obertes i glutis actius.</t>
+  </si>
+  <si>
     <t>ex_suitcase_carry</t>
   </si>
   <si>
@@ -780,6 +861,9 @@
     <t>carry; antiinclinació</t>
   </si>
   <si>
+    <t>Camina sostenint una càrrega només a un costat, mantenint tronc vertical i pelvis estable sense inclinar-te cap al pes o allunyar-te’n.</t>
+  </si>
+  <si>
     <t>ex_one_arm_cable_row</t>
   </si>
   <si>
@@ -795,6 +879,9 @@
     <t>tracció; unilateral</t>
   </si>
   <si>
+    <t>Davant d’una politja, agafa amb una mà i porta el colze enrere fins apropar la mà al costat del tronc, evitant rotar.</t>
+  </si>
+  <si>
     <t>ex_calf_raise</t>
   </si>
   <si>
@@ -816,6 +903,9 @@
     <t>bessons</t>
   </si>
   <si>
+    <t>Eleva els talons fins quedar sobre les puntes dels peus, fes una breu pausa a dalt i baixa lentament fins recuperar el rang inicial.</t>
+  </si>
+  <si>
     <t>Hi ha variants bilaterals i unilaterals als plans</t>
   </si>
   <si>
@@ -834,6 +924,9 @@
     <t>bessons; unilateral</t>
   </si>
   <si>
+    <t>Sobre una sola cama, eleva el taló tant com puguis mantenint genoll i turmell alineats; baixa lentament abans de repetir.</t>
+  </si>
+  <si>
     <t>ex_face_pull</t>
   </si>
   <si>
@@ -852,6 +945,9 @@
     <t>escàpules; espatlla</t>
   </si>
   <si>
+    <t>Estira la corda o banda cap a la cara amb els colzes alts, separant les mans i portant les escàpules enrere sense encongir espatlles.</t>
+  </si>
+  <si>
     <t>ex_snap_down</t>
   </si>
   <si>
@@ -864,6 +960,9 @@
     <t>pliometria; aterratge</t>
   </si>
   <si>
+    <t>Des de puntes o posició alta, baixa ràpidament a una posició atlètica i frena de manera estable amb malucs i genolls flexionats.</t>
+  </si>
+  <si>
     <t>ex_drop_landing</t>
   </si>
   <si>
@@ -879,6 +978,9 @@
     <t>Caixa o step</t>
   </si>
   <si>
+    <t>Baixa d’un step o caixa sense impulsar-te, aterra amb els dos peus alhora i mantén la posició 2–3 segons amb genolls alineats.</t>
+  </si>
+  <si>
     <t>ex_single_leg_drop_landing</t>
   </si>
   <si>
@@ -900,6 +1002,9 @@
     <t>pliometria; unilateral</t>
   </si>
   <si>
+    <t>Baixa d’un step o caixa i aterra sobre una sola cama, absorbint l’impacte i estabilitzant maluc, genoll i turmell abans de repetir.</t>
+  </si>
+  <si>
     <t>ex_pogo_jumps</t>
   </si>
   <si>
@@ -924,6 +1029,9 @@
     <t>pliometria; reactiu</t>
   </si>
   <si>
+    <t>Fes petits salts verticals ràpids utilitzant sobretot el turmell, amb poc temps de contacte a terra i genolls lleument flexionats.</t>
+  </si>
+  <si>
     <t>ex_single_leg_hops</t>
   </si>
   <si>
@@ -942,6 +1050,9 @@
     <t>Salt unilateral</t>
   </si>
   <si>
+    <t>Salta repetidament sobre una sola cama mantenint salts curts i reactius, amb aterratges suaus i control de turmell i genoll.</t>
+  </si>
+  <si>
     <t>ex_reactive_lateral_jump</t>
   </si>
   <si>
@@ -966,6 +1077,9 @@
     <t>pliometria; reactiu; lateral</t>
   </si>
   <si>
+    <t>Fes petits salts ràpids d’un costat a l’altre, mantenint el cos estable i minimitzant el temps de contacte amb el terra.</t>
+  </si>
+  <si>
     <t>ex_pause_jump</t>
   </si>
   <si>
@@ -984,6 +1098,9 @@
     <t>pliometria; control</t>
   </si>
   <si>
+    <t>Salta i aterra amb control; després de cada aterratge fes una pausa estable abans de començar el salt següent.</t>
+  </si>
+  <si>
     <t>ex_isometric_squat</t>
   </si>
   <si>
@@ -1005,6 +1122,9 @@
     <t>isomètric; cames</t>
   </si>
   <si>
+    <t>Baixa a una posició d’esquat i mantén-la amb l’esquena neutra, genolls alineats i pes repartit sobre tot el peu.</t>
+  </si>
+  <si>
     <t>ex_hip_hike</t>
   </si>
   <si>
@@ -1029,6 +1149,9 @@
     <t>maluc; estabilitat</t>
   </si>
   <si>
+    <t>Dempeus sobre un step amb una cama lliure, deixa caure una mica la pelvis del costat lliure i torna a elevar-la amb el gluti de la cama de suport.</t>
+  </si>
+  <si>
     <t>ex_barbell_squat</t>
   </si>
   <si>
@@ -1050,6 +1173,9 @@
     <t>compost; cames</t>
   </si>
   <si>
+    <t>Amb la barra a l’esquena, baixa flexionant malucs i genolls mantenint el tronc estable i puja empenyent el terra amb els peus.</t>
+  </si>
+  <si>
     <t>ex_front_squat</t>
   </si>
   <si>
@@ -1068,6 +1194,9 @@
     <t>compost; frontal</t>
   </si>
   <si>
+    <t>Amb la barra davant de les espatlles i colzes alts, baixa en esquat mantenint el tronc vertical i puja sense deixar caure els colzes.</t>
+  </si>
+  <si>
     <t>ex_landmine_front_squat</t>
   </si>
   <si>
@@ -1086,6 +1215,9 @@
     <t>landmine; cames</t>
   </si>
   <si>
+    <t>Subjecta l’extrem de la barra davant del pit, baixa en esquat mantenint-la prop del cos i puja empenyent des de les cames.</t>
+  </si>
+  <si>
     <t>ex_burpee</t>
   </si>
   <si>
@@ -1104,6 +1236,9 @@
     <t>condicionament; pes corporal</t>
   </si>
   <si>
+    <t>Des de dempeus, baixa les mans a terra, porta els peus enrere a planxa, torna a recollir-los i incorpora’t; afegeix salt si correspon.</t>
+  </si>
+  <si>
     <t>ex_hamstring_bridge</t>
   </si>
   <si>
@@ -1125,6 +1260,9 @@
     <t>cadena posterior</t>
   </si>
   <si>
+    <t>Estirat boca amunt, recolza els talons a terra o en un suport, eleva la pelvis i mantén tensió als isquiotibials durant el moviment.</t>
+  </si>
+  <si>
     <t>ex_barbell_curl</t>
   </si>
   <si>
@@ -1149,6 +1287,9 @@
     <t>braços</t>
   </si>
   <si>
+    <t>Dempeus amb la barra, mantén els colzes prop del cos i flexiona’ls per pujar la barra; baixa-la lentament sense balancejar el tronc.</t>
+  </si>
+  <si>
     <t>ex_triceps_pushdown</t>
   </si>
   <si>
@@ -1170,6 +1311,9 @@
     <t>tríceps; politja</t>
   </si>
   <si>
+    <t>Davant d’una politja alta, mantén els colzes enganxats al cos i estira els braços cap avall fins bloquejar-los suaument; torna controlant.</t>
+  </si>
+  <si>
     <t>ex_single_arm_cable_lateral_raise</t>
   </si>
   <si>
@@ -1191,6 +1335,9 @@
     <t>espatlla; unilateral</t>
   </si>
   <si>
+    <t>De costat a una politja baixa, eleva el braç lateralment fins aproximadament l’altura de l’espatlla sense encongir-la ni inclinar el tronc.</t>
+  </si>
+  <si>
     <t>Apareix com a alternativa en pla previ</t>
   </si>
   <si>
@@ -1215,6 +1362,9 @@
     <t>pliometria tren superior</t>
   </si>
   <si>
+    <t>Baixa com en una flexió i empeny amb prou força perquè les mans perdin contacte amb el terra; aterra amb colzes flexionats i control.</t>
+  </si>
+  <si>
     <t>ex_sissy_squat</t>
   </si>
   <si>
@@ -1230,6 +1380,9 @@
     <t>quàdriceps</t>
   </si>
   <si>
+    <t>Amb suport si cal, mantén malucs estesos i inclina el cos enrere flexionant sobretot els genolls; torna contraient els quàdriceps.</t>
+  </si>
+  <si>
     <t>ex_unilateral_hip_thrust</t>
   </si>
   <si>
@@ -1245,6 +1398,9 @@
     <t>glutis; unilateral</t>
   </si>
   <si>
+    <t>Recolza l’esquena en un banc i treballa amb una sola cama: eleva la pelvis amb el gluti de la cama de suport i baixa controlant.</t>
+  </si>
+  <si>
     <t>ex_reverse_crunch</t>
   </si>
   <si>
@@ -1269,6 +1425,9 @@
     <t>core; pes corporal</t>
   </si>
   <si>
+    <t>Estirat boca amunt, porta els genolls cap al pit i eleva lleument la pelvis del terra amb l’abdomen; baixa sense deixar caure les cames.</t>
+  </si>
+  <si>
     <t>ex_wall_pec_stretch</t>
   </si>
   <si>
@@ -1290,6 +1449,9 @@
     <t>estirament; espatlla</t>
   </si>
   <si>
+    <t>Col·loca l’avantbraç o mà a la paret, gira suaument el tronc en sentit contrari fins notar tensió al pectoral sense forçar l’espatlla.</t>
+  </si>
+  <si>
     <t>ex_supported_lat_stretch</t>
   </si>
   <si>
@@ -1317,6 +1479,9 @@
     <t>estirament; dorsal</t>
   </si>
   <si>
+    <t>Recolza mans o colzes en un suport, porta els malucs enrere i deixa baixar el pit fins notar estirament als dorsals i espatlles.</t>
+  </si>
+  <si>
     <t>ex_hamstring_stretch</t>
   </si>
   <si>
@@ -1338,6 +1503,9 @@
     <t>estirament; cadena posterior</t>
   </si>
   <si>
+    <t>Allarga una cama i inclina el tronc des del maluc mantenint l’esquena neutra fins notar tensió als isquiotibials, sense rebots.</t>
+  </si>
+  <si>
     <t>ex_glute_stretch</t>
   </si>
   <si>
@@ -1356,6 +1524,9 @@
     <t>estirament; maluc</t>
   </si>
   <si>
+    <t>Creua o apropa una cama cap al tronc i porta suaument el genoll cap al pit fins notar l’estirament al gluti; mantén sense forçar.</t>
+  </si>
+  <si>
     <t>ex_calf_stretch</t>
   </si>
   <si>
@@ -1374,6 +1545,9 @@
     <t>estirament; turmell</t>
   </si>
   <si>
+    <t>Recolza les mans a la paret, porta una cama enrere amb el taló a terra i avança el cos fins notar tensió al bessó.</t>
+  </si>
+  <si>
     <t>ex_open_book</t>
   </si>
   <si>
@@ -1395,6 +1569,9 @@
     <t>mobilitat toràcica</t>
   </si>
   <si>
+    <t>Estirat de costat amb genolls flexionats, obre el braç superior cap enrere seguint-lo amb la mirada mentre mantens genolls junts.</t>
+  </si>
+  <si>
     <t>ex_quadruped_thoracic_rotation</t>
   </si>
   <si>
@@ -1410,6 +1587,9 @@
     <t>Quadrupèdia</t>
   </si>
   <si>
+    <t>En quadrupèdia, posa una mà al clatell o sota el cos i rota el tòrax obrint el colze cap al sostre sense desplaçar gaire la pelvis.</t>
+  </si>
+  <si>
     <t>ex_wall_thoracic_extension</t>
   </si>
   <si>
@@ -1425,6 +1605,9 @@
     <t>Extensió toràcica</t>
   </si>
   <si>
+    <t>Davant d’una paret, porta braços o colzes al suport i deixa baixar el pit mentre estens la columna toràcica sense arquejar en excés la zona lumbar.</t>
+  </si>
+  <si>
     <t>ex_thoracic_rotation</t>
   </si>
   <si>
@@ -1437,6 +1620,9 @@
     <t>Maluc</t>
   </si>
   <si>
+    <t>Des d’una posició estable, gira el tòrax cap a un costat mantenint la pelvis tan quieta com sigui possible i torna lentament al centre.</t>
+  </si>
+  <si>
     <t>ex_band_external_rotation</t>
   </si>
   <si>
@@ -1458,6 +1644,9 @@
     <t>manguit rotador; banda</t>
   </si>
   <si>
+    <t>Amb el colze enganxat al cos i flexionat a 90°, gira l’avantbraç cap enfora contra la banda sense separar el colze.</t>
+  </si>
+  <si>
     <t>ex_glute_bridge_pause</t>
   </si>
   <si>
@@ -1473,6 +1662,9 @@
     <t>activació glutis</t>
   </si>
   <si>
+    <t>Estirat boca amunt amb genolls flexionats, eleva la pelvis, contrau glutis i mantén una breu pausa a dalt abans de baixar controladament.</t>
+  </si>
+  <si>
     <t>ex_low_skipping</t>
   </si>
   <si>
@@ -1494,6 +1686,9 @@
     <t>dinàmic; activació</t>
   </si>
   <si>
+    <t>Fes passos curts i ràpids elevant poc els genolls, amb contacte lleuger del peu i augmentant progressivament el ritme sense esprintar.</t>
+  </si>
+  <si>
     <t>ex_lateral_shuffle</t>
   </si>
   <si>
@@ -1515,6 +1710,9 @@
     <t>dinàmic; lateral; pàdel</t>
   </si>
   <si>
+    <t>En posició atlètica, desplaça’t lateralment amb passos curts sense creuar els peus, mantenint genolls flexionats i tronc estable.</t>
+  </si>
+  <si>
     <t>ex_short_acceleration</t>
   </si>
   <si>
@@ -1534,6 +1732,9 @@
   </si>
   <si>
     <t>dinàmic; acceleració; pàdel</t>
+  </si>
+  <si>
+    <t>Des d’una posició preparada, accelera de manera progressiva durant 3–4 metres amb passes curtes al principi i sense arribar a un esprint màxim.</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1780,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1588,6 +1789,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1827,7 +2031,8 @@
     <col customWidth="1" min="15" max="15" width="10.13"/>
     <col customWidth="1" min="16" max="16" width="21.38"/>
     <col customWidth="1" min="17" max="17" width="22.25"/>
-    <col customWidth="1" min="18" max="21" width="27.63"/>
+    <col customWidth="1" min="18" max="18" width="45.13"/>
+    <col customWidth="1" min="19" max="21" width="27.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1894,6129 +2099,6339 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="U3" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="P8" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N18" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>174</v>
+        <v>191</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="Q21" s="2" t="s">
-        <v>201</v>
+        <v>221</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>222</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>217</v>
+        <v>239</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>223</v>
+        <v>246</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>174</v>
+        <v>191</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>245</v>
+        <v>271</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>272</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>254</v>
+        <v>281</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>282</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>259</v>
+        <v>287</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>266</v>
+        <v>295</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>272</v>
+        <v>302</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>303</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>278</v>
+        <v>309</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>282</v>
+        <v>314</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>294</v>
+        <v>328</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>302</v>
+        <v>337</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>338</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>294</v>
+        <v>328</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>316</v>
+        <v>353</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>322</v>
+        <v>360</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>326</v>
+        <v>365</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>329</v>
+        <v>368</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>369</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>332</v>
+        <v>372</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>333</v>
+        <v>373</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>334</v>
+        <v>374</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>335</v>
+        <v>375</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>336</v>
+        <v>376</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>337</v>
+        <v>377</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>344</v>
+        <v>385</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>386</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>350</v>
+        <v>392</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>393</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>356</v>
+        <v>399</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>400</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>358</v>
+        <v>402</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>358</v>
+        <v>402</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>362</v>
+        <v>406</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>407</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>364</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>366</v>
+        <v>411</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>369</v>
+        <v>414</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>415</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>370</v>
+        <v>416</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>371</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>372</v>
+        <v>418</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>375</v>
+        <v>421</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>376</v>
+        <v>422</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>377</v>
+        <v>423</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>378</v>
+        <v>425</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>379</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>380</v>
+        <v>427</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>381</v>
+        <v>428</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>382</v>
+        <v>429</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>384</v>
+        <v>431</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>432</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>385</v>
+        <v>433</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>391</v>
+        <v>439</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>392</v>
+        <v>441</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>393</v>
+        <v>442</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>395</v>
+        <v>444</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>397</v>
+        <v>446</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>398</v>
+        <v>447</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>399</v>
+        <v>448</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>449</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>392</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>402</v>
+        <v>452</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>403</v>
+        <v>453</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>404</v>
+        <v>454</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>455</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>406</v>
+        <v>457</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>407</v>
+        <v>458</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>409</v>
+        <v>460</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>410</v>
+        <v>462</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>411</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>413</v>
+        <v>465</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>414</v>
+        <v>466</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>415</v>
+        <v>467</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>416</v>
+        <v>468</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>417</v>
+        <v>469</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>470</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>421</v>
+        <v>474</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>423</v>
+        <v>476</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>424</v>
+        <v>477</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>478</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>425</v>
+        <v>479</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>426</v>
+        <v>480</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>427</v>
+        <v>481</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>428</v>
+        <v>482</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>429</v>
+        <v>483</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>431</v>
+        <v>485</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>432</v>
+        <v>486</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>433</v>
+        <v>487</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>488</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>434</v>
+        <v>489</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>435</v>
+        <v>490</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>436</v>
+        <v>491</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>437</v>
+        <v>492</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>438</v>
+        <v>493</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>439</v>
+        <v>494</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>440</v>
+        <v>495</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>496</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>441</v>
+        <v>497</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>443</v>
+        <v>499</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>444</v>
+        <v>500</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>445</v>
+        <v>501</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>446</v>
+        <v>502</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>503</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>447</v>
+        <v>504</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>448</v>
+        <v>505</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>449</v>
+        <v>506</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>450</v>
+        <v>507</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>451</v>
+        <v>508</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>452</v>
+        <v>509</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>453</v>
+        <v>511</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>458</v>
+        <v>516</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>459</v>
+        <v>517</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>518</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>460</v>
+        <v>519</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>463</v>
+        <v>522</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>464</v>
+        <v>523</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>459</v>
+        <v>517</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>524</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>465</v>
+        <v>525</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>466</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>467</v>
+        <v>527</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>468</v>
+        <v>528</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>429</v>
+        <v>483</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>469</v>
+        <v>529</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>459</v>
+        <v>517</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>530</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>470</v>
+        <v>531</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>471</v>
+        <v>532</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>472</v>
+        <v>533</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>473</v>
+        <v>534</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>459</v>
+        <v>517</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>474</v>
+        <v>536</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>475</v>
+        <v>537</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>476</v>
+        <v>538</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>477</v>
+        <v>539</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>478</v>
+        <v>540</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>479</v>
+        <v>541</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>480</v>
+        <v>542</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>543</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>481</v>
+        <v>544</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>482</v>
+        <v>545</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>483</v>
+        <v>546</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>485</v>
+        <v>548</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>549</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>486</v>
+        <v>550</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>487</v>
+        <v>551</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>488</v>
+        <v>552</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>489</v>
+        <v>553</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>490</v>
+        <v>554</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>491</v>
+        <v>555</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>492</v>
+        <v>556</v>
+      </c>
+      <c r="R65" s="3" t="s">
+        <v>557</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>493</v>
+        <v>558</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>494</v>
+        <v>559</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>495</v>
+        <v>560</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>496</v>
+        <v>561</v>
       </c>
       <c r="F66" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P66" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="Q66" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>33</v>
+        <v>564</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="T66" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>500</v>
+        <v>566</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>501</v>
+        <v>567</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>502</v>
+        <v>568</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>503</v>
+        <v>569</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>505</v>
+        <v>571</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="T67" s="3" t="s">
-        <v>33</v>
+        <v>572</v>
+      </c>
+      <c r="R67" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="T67" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="68">
-      <c r="T68" s="4"/>
+      <c r="T68" s="5"/>
     </row>
     <row r="69">
-      <c r="T69" s="4"/>
+      <c r="T69" s="5"/>
     </row>
     <row r="70">
-      <c r="T70" s="4"/>
+      <c r="T70" s="5"/>
     </row>
     <row r="71">
-      <c r="T71" s="4"/>
+      <c r="T71" s="5"/>
     </row>
     <row r="72">
-      <c r="T72" s="4"/>
+      <c r="T72" s="5"/>
     </row>
     <row r="73">
-      <c r="T73" s="4"/>
+      <c r="T73" s="5"/>
     </row>
     <row r="74">
-      <c r="T74" s="4"/>
+      <c r="T74" s="5"/>
     </row>
     <row r="75">
-      <c r="T75" s="4"/>
+      <c r="T75" s="5"/>
     </row>
     <row r="76">
-      <c r="T76" s="4"/>
+      <c r="T76" s="5"/>
     </row>
     <row r="77">
-      <c r="T77" s="4"/>
+      <c r="T77" s="5"/>
     </row>
     <row r="78">
-      <c r="T78" s="4"/>
+      <c r="T78" s="5"/>
     </row>
     <row r="79">
-      <c r="T79" s="4"/>
+      <c r="T79" s="5"/>
     </row>
     <row r="80">
-      <c r="T80" s="4"/>
+      <c r="T80" s="5"/>
     </row>
     <row r="81">
-      <c r="T81" s="4"/>
+      <c r="T81" s="5"/>
     </row>
     <row r="82">
-      <c r="T82" s="4"/>
+      <c r="T82" s="5"/>
     </row>
     <row r="83">
-      <c r="T83" s="4"/>
+      <c r="T83" s="5"/>
     </row>
     <row r="84">
-      <c r="T84" s="4"/>
+      <c r="T84" s="5"/>
     </row>
     <row r="85">
-      <c r="T85" s="4"/>
+      <c r="T85" s="5"/>
     </row>
     <row r="86">
-      <c r="T86" s="4"/>
+      <c r="T86" s="5"/>
     </row>
     <row r="87">
-      <c r="T87" s="4"/>
+      <c r="T87" s="5"/>
     </row>
     <row r="88">
-      <c r="T88" s="4"/>
+      <c r="T88" s="5"/>
     </row>
     <row r="89">
-      <c r="T89" s="4"/>
+      <c r="T89" s="5"/>
     </row>
     <row r="90">
-      <c r="T90" s="4"/>
+      <c r="T90" s="5"/>
     </row>
     <row r="91">
-      <c r="T91" s="4"/>
+      <c r="T91" s="5"/>
     </row>
     <row r="92">
-      <c r="T92" s="4"/>
+      <c r="T92" s="5"/>
     </row>
     <row r="93">
-      <c r="T93" s="4"/>
+      <c r="T93" s="5"/>
     </row>
     <row r="94">
-      <c r="T94" s="4"/>
+      <c r="T94" s="5"/>
     </row>
     <row r="95">
-      <c r="T95" s="4"/>
+      <c r="T95" s="5"/>
     </row>
     <row r="96">
-      <c r="T96" s="4"/>
+      <c r="T96" s="5"/>
     </row>
     <row r="97">
-      <c r="T97" s="4"/>
+      <c r="T97" s="5"/>
     </row>
     <row r="98">
-      <c r="T98" s="4"/>
+      <c r="T98" s="5"/>
     </row>
     <row r="99">
-      <c r="T99" s="4"/>
+      <c r="T99" s="5"/>
     </row>
     <row r="100">
-      <c r="T100" s="4"/>
+      <c r="T100" s="5"/>
     </row>
     <row r="101">
-      <c r="T101" s="4"/>
+      <c r="T101" s="5"/>
     </row>
     <row r="102">
-      <c r="T102" s="4"/>
+      <c r="T102" s="5"/>
     </row>
     <row r="103">
-      <c r="T103" s="4"/>
+      <c r="T103" s="5"/>
     </row>
     <row r="104">
-      <c r="T104" s="4"/>
+      <c r="T104" s="5"/>
     </row>
     <row r="105">
-      <c r="T105" s="4"/>
+      <c r="T105" s="5"/>
     </row>
     <row r="106">
-      <c r="T106" s="4"/>
+      <c r="T106" s="5"/>
     </row>
     <row r="107">
-      <c r="T107" s="4"/>
+      <c r="T107" s="5"/>
     </row>
     <row r="108">
-      <c r="T108" s="4"/>
+      <c r="T108" s="5"/>
     </row>
     <row r="109">
-      <c r="T109" s="4"/>
+      <c r="T109" s="5"/>
     </row>
     <row r="110">
-      <c r="T110" s="4"/>
+      <c r="T110" s="5"/>
     </row>
     <row r="111">
-      <c r="T111" s="4"/>
+      <c r="T111" s="5"/>
     </row>
     <row r="112">
-      <c r="T112" s="4"/>
+      <c r="T112" s="5"/>
     </row>
     <row r="113">
-      <c r="T113" s="4"/>
+      <c r="T113" s="5"/>
     </row>
     <row r="114">
-      <c r="T114" s="4"/>
+      <c r="T114" s="5"/>
     </row>
     <row r="115">
-      <c r="T115" s="4"/>
+      <c r="T115" s="5"/>
     </row>
     <row r="116">
-      <c r="T116" s="4"/>
+      <c r="T116" s="5"/>
     </row>
     <row r="117">
-      <c r="T117" s="4"/>
+      <c r="T117" s="5"/>
     </row>
     <row r="118">
-      <c r="T118" s="4"/>
+      <c r="T118" s="5"/>
     </row>
     <row r="119">
-      <c r="T119" s="4"/>
+      <c r="T119" s="5"/>
     </row>
     <row r="120">
-      <c r="T120" s="4"/>
+      <c r="T120" s="5"/>
     </row>
     <row r="121">
-      <c r="T121" s="4"/>
+      <c r="T121" s="5"/>
     </row>
     <row r="122">
-      <c r="T122" s="4"/>
+      <c r="T122" s="5"/>
     </row>
     <row r="123">
-      <c r="T123" s="4"/>
+      <c r="T123" s="5"/>
     </row>
     <row r="124">
-      <c r="T124" s="4"/>
+      <c r="T124" s="5"/>
     </row>
     <row r="125">
-      <c r="T125" s="4"/>
+      <c r="T125" s="5"/>
     </row>
     <row r="126">
-      <c r="T126" s="4"/>
+      <c r="T126" s="5"/>
     </row>
     <row r="127">
-      <c r="T127" s="4"/>
+      <c r="T127" s="5"/>
     </row>
     <row r="128">
-      <c r="T128" s="4"/>
+      <c r="T128" s="5"/>
     </row>
     <row r="129">
-      <c r="T129" s="4"/>
+      <c r="T129" s="5"/>
     </row>
     <row r="130">
-      <c r="T130" s="4"/>
+      <c r="T130" s="5"/>
     </row>
     <row r="131">
-      <c r="T131" s="4"/>
+      <c r="T131" s="5"/>
     </row>
     <row r="132">
-      <c r="T132" s="4"/>
+      <c r="T132" s="5"/>
     </row>
     <row r="133">
-      <c r="T133" s="4"/>
+      <c r="T133" s="5"/>
     </row>
     <row r="134">
-      <c r="T134" s="4"/>
+      <c r="T134" s="5"/>
     </row>
     <row r="135">
-      <c r="T135" s="4"/>
+      <c r="T135" s="5"/>
     </row>
     <row r="136">
-      <c r="T136" s="4"/>
+      <c r="T136" s="5"/>
     </row>
     <row r="137">
-      <c r="T137" s="4"/>
+      <c r="T137" s="5"/>
     </row>
     <row r="138">
-      <c r="T138" s="4"/>
+      <c r="T138" s="5"/>
     </row>
     <row r="139">
-      <c r="T139" s="4"/>
+      <c r="T139" s="5"/>
     </row>
     <row r="140">
-      <c r="T140" s="4"/>
+      <c r="T140" s="5"/>
     </row>
     <row r="141">
-      <c r="T141" s="4"/>
+      <c r="T141" s="5"/>
     </row>
     <row r="142">
-      <c r="T142" s="4"/>
+      <c r="T142" s="5"/>
     </row>
     <row r="143">
-      <c r="T143" s="4"/>
+      <c r="T143" s="5"/>
     </row>
     <row r="144">
-      <c r="T144" s="4"/>
+      <c r="T144" s="5"/>
     </row>
     <row r="145">
-      <c r="T145" s="4"/>
+      <c r="T145" s="5"/>
     </row>
     <row r="146">
-      <c r="T146" s="4"/>
+      <c r="T146" s="5"/>
     </row>
     <row r="147">
-      <c r="T147" s="4"/>
+      <c r="T147" s="5"/>
     </row>
     <row r="148">
-      <c r="T148" s="4"/>
+      <c r="T148" s="5"/>
     </row>
     <row r="149">
-      <c r="T149" s="4"/>
+      <c r="T149" s="5"/>
     </row>
     <row r="150">
-      <c r="T150" s="4"/>
+      <c r="T150" s="5"/>
     </row>
     <row r="151">
-      <c r="T151" s="4"/>
+      <c r="T151" s="5"/>
     </row>
     <row r="152">
-      <c r="T152" s="4"/>
+      <c r="T152" s="5"/>
     </row>
     <row r="153">
-      <c r="T153" s="4"/>
+      <c r="T153" s="5"/>
     </row>
     <row r="154">
-      <c r="T154" s="4"/>
+      <c r="T154" s="5"/>
     </row>
     <row r="155">
-      <c r="T155" s="4"/>
+      <c r="T155" s="5"/>
     </row>
     <row r="156">
-      <c r="T156" s="4"/>
+      <c r="T156" s="5"/>
     </row>
     <row r="157">
-      <c r="T157" s="4"/>
+      <c r="T157" s="5"/>
     </row>
     <row r="158">
-      <c r="T158" s="4"/>
+      <c r="T158" s="5"/>
     </row>
     <row r="159">
-      <c r="T159" s="4"/>
+      <c r="T159" s="5"/>
     </row>
     <row r="160">
-      <c r="T160" s="4"/>
+      <c r="T160" s="5"/>
     </row>
     <row r="161">
-      <c r="T161" s="4"/>
+      <c r="T161" s="5"/>
     </row>
     <row r="162">
-      <c r="T162" s="4"/>
+      <c r="T162" s="5"/>
     </row>
     <row r="163">
-      <c r="T163" s="4"/>
+      <c r="T163" s="5"/>
     </row>
     <row r="164">
-      <c r="T164" s="4"/>
+      <c r="T164" s="5"/>
     </row>
     <row r="165">
-      <c r="T165" s="4"/>
+      <c r="T165" s="5"/>
     </row>
     <row r="166">
-      <c r="T166" s="4"/>
+      <c r="T166" s="5"/>
     </row>
     <row r="167">
-      <c r="T167" s="4"/>
+      <c r="T167" s="5"/>
     </row>
     <row r="168">
-      <c r="T168" s="4"/>
+      <c r="T168" s="5"/>
     </row>
     <row r="169">
-      <c r="T169" s="4"/>
+      <c r="T169" s="5"/>
     </row>
     <row r="170">
-      <c r="T170" s="4"/>
+      <c r="T170" s="5"/>
     </row>
     <row r="171">
-      <c r="T171" s="4"/>
+      <c r="T171" s="5"/>
     </row>
     <row r="172">
-      <c r="T172" s="4"/>
+      <c r="T172" s="5"/>
     </row>
     <row r="173">
-      <c r="T173" s="4"/>
+      <c r="T173" s="5"/>
     </row>
     <row r="174">
-      <c r="T174" s="4"/>
+      <c r="T174" s="5"/>
     </row>
     <row r="175">
-      <c r="T175" s="4"/>
+      <c r="T175" s="5"/>
     </row>
     <row r="176">
-      <c r="T176" s="4"/>
+      <c r="T176" s="5"/>
     </row>
     <row r="177">
-      <c r="T177" s="4"/>
+      <c r="T177" s="5"/>
     </row>
     <row r="178">
-      <c r="T178" s="4"/>
+      <c r="T178" s="5"/>
     </row>
     <row r="179">
-      <c r="T179" s="4"/>
+      <c r="T179" s="5"/>
     </row>
     <row r="180">
-      <c r="T180" s="4"/>
+      <c r="T180" s="5"/>
     </row>
     <row r="181">
-      <c r="T181" s="4"/>
+      <c r="T181" s="5"/>
     </row>
     <row r="182">
-      <c r="T182" s="4"/>
+      <c r="T182" s="5"/>
     </row>
     <row r="183">
-      <c r="T183" s="4"/>
+      <c r="T183" s="5"/>
     </row>
     <row r="184">
-      <c r="T184" s="4"/>
+      <c r="T184" s="5"/>
     </row>
     <row r="185">
-      <c r="T185" s="4"/>
+      <c r="T185" s="5"/>
     </row>
     <row r="186">
-      <c r="T186" s="4"/>
+      <c r="T186" s="5"/>
     </row>
     <row r="187">
-      <c r="T187" s="4"/>
+      <c r="T187" s="5"/>
     </row>
     <row r="188">
-      <c r="T188" s="4"/>
+      <c r="T188" s="5"/>
     </row>
     <row r="189">
-      <c r="T189" s="4"/>
+      <c r="T189" s="5"/>
     </row>
     <row r="190">
-      <c r="T190" s="4"/>
+      <c r="T190" s="5"/>
     </row>
     <row r="191">
-      <c r="T191" s="4"/>
+      <c r="T191" s="5"/>
     </row>
     <row r="192">
-      <c r="T192" s="4"/>
+      <c r="T192" s="5"/>
     </row>
     <row r="193">
-      <c r="T193" s="4"/>
+      <c r="T193" s="5"/>
     </row>
     <row r="194">
-      <c r="T194" s="4"/>
+      <c r="T194" s="5"/>
     </row>
     <row r="195">
-      <c r="T195" s="4"/>
+      <c r="T195" s="5"/>
     </row>
     <row r="196">
-      <c r="T196" s="4"/>
+      <c r="T196" s="5"/>
     </row>
     <row r="197">
-      <c r="T197" s="4"/>
+      <c r="T197" s="5"/>
     </row>
     <row r="198">
-      <c r="T198" s="4"/>
+      <c r="T198" s="5"/>
     </row>
     <row r="199">
-      <c r="T199" s="4"/>
+      <c r="T199" s="5"/>
     </row>
     <row r="200">
-      <c r="T200" s="4"/>
+      <c r="T200" s="5"/>
     </row>
     <row r="201">
-      <c r="T201" s="4"/>
+      <c r="T201" s="5"/>
     </row>
     <row r="202">
-      <c r="T202" s="4"/>
+      <c r="T202" s="5"/>
     </row>
     <row r="203">
-      <c r="T203" s="4"/>
+      <c r="T203" s="5"/>
     </row>
     <row r="204">
-      <c r="T204" s="4"/>
+      <c r="T204" s="5"/>
     </row>
     <row r="205">
-      <c r="T205" s="4"/>
+      <c r="T205" s="5"/>
     </row>
     <row r="206">
-      <c r="T206" s="4"/>
+      <c r="T206" s="5"/>
     </row>
     <row r="207">
-      <c r="T207" s="4"/>
+      <c r="T207" s="5"/>
     </row>
     <row r="208">
-      <c r="T208" s="4"/>
+      <c r="T208" s="5"/>
     </row>
     <row r="209">
-      <c r="T209" s="4"/>
+      <c r="T209" s="5"/>
     </row>
     <row r="210">
-      <c r="T210" s="4"/>
+      <c r="T210" s="5"/>
     </row>
     <row r="211">
-      <c r="T211" s="4"/>
+      <c r="T211" s="5"/>
     </row>
     <row r="212">
-      <c r="T212" s="4"/>
+      <c r="T212" s="5"/>
     </row>
     <row r="213">
-      <c r="T213" s="4"/>
+      <c r="T213" s="5"/>
     </row>
     <row r="214">
-      <c r="T214" s="4"/>
+      <c r="T214" s="5"/>
     </row>
     <row r="215">
-      <c r="T215" s="4"/>
+      <c r="T215" s="5"/>
     </row>
     <row r="216">
-      <c r="T216" s="4"/>
+      <c r="T216" s="5"/>
     </row>
     <row r="217">
-      <c r="T217" s="4"/>
+      <c r="T217" s="5"/>
     </row>
     <row r="218">
-      <c r="T218" s="4"/>
+      <c r="T218" s="5"/>
     </row>
     <row r="219">
-      <c r="T219" s="4"/>
+      <c r="T219" s="5"/>
     </row>
     <row r="220">
-      <c r="T220" s="4"/>
+      <c r="T220" s="5"/>
     </row>
     <row r="221">
-      <c r="T221" s="4"/>
+      <c r="T221" s="5"/>
     </row>
     <row r="222">
-      <c r="T222" s="4"/>
+      <c r="T222" s="5"/>
     </row>
     <row r="223">
-      <c r="T223" s="4"/>
+      <c r="T223" s="5"/>
     </row>
     <row r="224">
-      <c r="T224" s="4"/>
+      <c r="T224" s="5"/>
     </row>
     <row r="225">
-      <c r="T225" s="4"/>
+      <c r="T225" s="5"/>
     </row>
     <row r="226">
-      <c r="T226" s="4"/>
+      <c r="T226" s="5"/>
     </row>
     <row r="227">
-      <c r="T227" s="4"/>
+      <c r="T227" s="5"/>
     </row>
     <row r="228">
-      <c r="T228" s="4"/>
+      <c r="T228" s="5"/>
     </row>
     <row r="229">
-      <c r="T229" s="4"/>
+      <c r="T229" s="5"/>
     </row>
     <row r="230">
-      <c r="T230" s="4"/>
+      <c r="T230" s="5"/>
     </row>
     <row r="231">
-      <c r="T231" s="4"/>
+      <c r="T231" s="5"/>
     </row>
     <row r="232">
-      <c r="T232" s="4"/>
+      <c r="T232" s="5"/>
     </row>
     <row r="233">
-      <c r="T233" s="4"/>
+      <c r="T233" s="5"/>
     </row>
     <row r="234">
-      <c r="T234" s="4"/>
+      <c r="T234" s="5"/>
     </row>
     <row r="235">
-      <c r="T235" s="4"/>
+      <c r="T235" s="5"/>
     </row>
     <row r="236">
-      <c r="T236" s="4"/>
+      <c r="T236" s="5"/>
     </row>
     <row r="237">
-      <c r="T237" s="4"/>
+      <c r="T237" s="5"/>
     </row>
     <row r="238">
-      <c r="T238" s="4"/>
+      <c r="T238" s="5"/>
     </row>
     <row r="239">
-      <c r="T239" s="4"/>
+      <c r="T239" s="5"/>
     </row>
     <row r="240">
-      <c r="T240" s="4"/>
+      <c r="T240" s="5"/>
     </row>
     <row r="241">
-      <c r="T241" s="4"/>
+      <c r="T241" s="5"/>
     </row>
     <row r="242">
-      <c r="T242" s="4"/>
+      <c r="T242" s="5"/>
     </row>
     <row r="243">
-      <c r="T243" s="4"/>
+      <c r="T243" s="5"/>
     </row>
     <row r="244">
-      <c r="T244" s="4"/>
+      <c r="T244" s="5"/>
     </row>
     <row r="245">
-      <c r="T245" s="4"/>
+      <c r="T245" s="5"/>
     </row>
     <row r="246">
-      <c r="T246" s="4"/>
+      <c r="T246" s="5"/>
     </row>
     <row r="247">
-      <c r="T247" s="4"/>
+      <c r="T247" s="5"/>
     </row>
     <row r="248">
-      <c r="T248" s="4"/>
+      <c r="T248" s="5"/>
     </row>
     <row r="249">
-      <c r="T249" s="4"/>
+      <c r="T249" s="5"/>
     </row>
     <row r="250">
-      <c r="T250" s="4"/>
+      <c r="T250" s="5"/>
     </row>
     <row r="251">
-      <c r="T251" s="4"/>
+      <c r="T251" s="5"/>
     </row>
     <row r="252">
-      <c r="T252" s="4"/>
+      <c r="T252" s="5"/>
     </row>
     <row r="253">
-      <c r="T253" s="4"/>
+      <c r="T253" s="5"/>
     </row>
     <row r="254">
-      <c r="T254" s="4"/>
+      <c r="T254" s="5"/>
     </row>
     <row r="255">
-      <c r="T255" s="4"/>
+      <c r="T255" s="5"/>
     </row>
     <row r="256">
-      <c r="T256" s="4"/>
+      <c r="T256" s="5"/>
     </row>
     <row r="257">
-      <c r="T257" s="4"/>
+      <c r="T257" s="5"/>
     </row>
     <row r="258">
-      <c r="T258" s="4"/>
+      <c r="T258" s="5"/>
     </row>
     <row r="259">
-      <c r="T259" s="4"/>
+      <c r="T259" s="5"/>
     </row>
     <row r="260">
-      <c r="T260" s="4"/>
+      <c r="T260" s="5"/>
     </row>
     <row r="261">
-      <c r="T261" s="4"/>
+      <c r="T261" s="5"/>
     </row>
     <row r="262">
-      <c r="T262" s="4"/>
+      <c r="T262" s="5"/>
     </row>
     <row r="263">
-      <c r="T263" s="4"/>
+      <c r="T263" s="5"/>
     </row>
     <row r="264">
-      <c r="T264" s="4"/>
+      <c r="T264" s="5"/>
     </row>
     <row r="265">
-      <c r="T265" s="4"/>
+      <c r="T265" s="5"/>
     </row>
     <row r="266">
-      <c r="T266" s="4"/>
+      <c r="T266" s="5"/>
     </row>
     <row r="267">
-      <c r="T267" s="4"/>
+      <c r="T267" s="5"/>
     </row>
     <row r="268">
-      <c r="T268" s="4"/>
+      <c r="T268" s="5"/>
     </row>
     <row r="269">
-      <c r="T269" s="4"/>
+      <c r="T269" s="5"/>
     </row>
     <row r="270">
-      <c r="T270" s="4"/>
+      <c r="T270" s="5"/>
     </row>
     <row r="271">
-      <c r="T271" s="4"/>
+      <c r="T271" s="5"/>
     </row>
     <row r="272">
-      <c r="T272" s="4"/>
+      <c r="T272" s="5"/>
     </row>
     <row r="273">
-      <c r="T273" s="4"/>
+      <c r="T273" s="5"/>
     </row>
     <row r="274">
-      <c r="T274" s="4"/>
+      <c r="T274" s="5"/>
     </row>
     <row r="275">
-      <c r="T275" s="4"/>
+      <c r="T275" s="5"/>
     </row>
     <row r="276">
-      <c r="T276" s="4"/>
+      <c r="T276" s="5"/>
     </row>
     <row r="277">
-      <c r="T277" s="4"/>
+      <c r="T277" s="5"/>
     </row>
     <row r="278">
-      <c r="T278" s="4"/>
+      <c r="T278" s="5"/>
     </row>
     <row r="279">
-      <c r="T279" s="4"/>
+      <c r="T279" s="5"/>
     </row>
     <row r="280">
-      <c r="T280" s="4"/>
+      <c r="T280" s="5"/>
     </row>
     <row r="281">
-      <c r="T281" s="4"/>
+      <c r="T281" s="5"/>
     </row>
     <row r="282">
-      <c r="T282" s="4"/>
+      <c r="T282" s="5"/>
     </row>
     <row r="283">
-      <c r="T283" s="4"/>
+      <c r="T283" s="5"/>
     </row>
     <row r="284">
-      <c r="T284" s="4"/>
+      <c r="T284" s="5"/>
     </row>
     <row r="285">
-      <c r="T285" s="4"/>
+      <c r="T285" s="5"/>
     </row>
     <row r="286">
-      <c r="T286" s="4"/>
+      <c r="T286" s="5"/>
     </row>
     <row r="287">
-      <c r="T287" s="4"/>
+      <c r="T287" s="5"/>
     </row>
     <row r="288">
-      <c r="T288" s="4"/>
+      <c r="T288" s="5"/>
     </row>
     <row r="289">
-      <c r="T289" s="4"/>
+      <c r="T289" s="5"/>
     </row>
     <row r="290">
-      <c r="T290" s="4"/>
+      <c r="T290" s="5"/>
     </row>
     <row r="291">
-      <c r="T291" s="4"/>
+      <c r="T291" s="5"/>
     </row>
     <row r="292">
-      <c r="T292" s="4"/>
+      <c r="T292" s="5"/>
     </row>
     <row r="293">
-      <c r="T293" s="4"/>
+      <c r="T293" s="5"/>
     </row>
     <row r="294">
-      <c r="T294" s="4"/>
+      <c r="T294" s="5"/>
     </row>
     <row r="295">
-      <c r="T295" s="4"/>
+      <c r="T295" s="5"/>
     </row>
     <row r="296">
-      <c r="T296" s="4"/>
+      <c r="T296" s="5"/>
     </row>
     <row r="297">
-      <c r="T297" s="4"/>
+      <c r="T297" s="5"/>
     </row>
     <row r="298">
-      <c r="T298" s="4"/>
+      <c r="T298" s="5"/>
     </row>
     <row r="299">
-      <c r="T299" s="4"/>
+      <c r="T299" s="5"/>
     </row>
     <row r="300">
-      <c r="T300" s="4"/>
+      <c r="T300" s="5"/>
     </row>
     <row r="301">
-      <c r="T301" s="4"/>
+      <c r="T301" s="5"/>
     </row>
     <row r="302">
-      <c r="T302" s="4"/>
+      <c r="T302" s="5"/>
     </row>
     <row r="303">
-      <c r="T303" s="4"/>
+      <c r="T303" s="5"/>
     </row>
     <row r="304">
-      <c r="T304" s="4"/>
+      <c r="T304" s="5"/>
     </row>
     <row r="305">
-      <c r="T305" s="4"/>
+      <c r="T305" s="5"/>
     </row>
     <row r="306">
-      <c r="T306" s="4"/>
+      <c r="T306" s="5"/>
     </row>
     <row r="307">
-      <c r="T307" s="4"/>
+      <c r="T307" s="5"/>
     </row>
     <row r="308">
-      <c r="T308" s="4"/>
+      <c r="T308" s="5"/>
     </row>
     <row r="309">
-      <c r="T309" s="4"/>
+      <c r="T309" s="5"/>
     </row>
     <row r="310">
-      <c r="T310" s="4"/>
+      <c r="T310" s="5"/>
     </row>
     <row r="311">
-      <c r="T311" s="4"/>
+      <c r="T311" s="5"/>
     </row>
     <row r="312">
-      <c r="T312" s="4"/>
+      <c r="T312" s="5"/>
     </row>
     <row r="313">
-      <c r="T313" s="4"/>
+      <c r="T313" s="5"/>
     </row>
     <row r="314">
-      <c r="T314" s="4"/>
+      <c r="T314" s="5"/>
     </row>
     <row r="315">
-      <c r="T315" s="4"/>
+      <c r="T315" s="5"/>
     </row>
     <row r="316">
-      <c r="T316" s="4"/>
+      <c r="T316" s="5"/>
     </row>
     <row r="317">
-      <c r="T317" s="4"/>
+      <c r="T317" s="5"/>
     </row>
     <row r="318">
-      <c r="T318" s="4"/>
+      <c r="T318" s="5"/>
     </row>
     <row r="319">
-      <c r="T319" s="4"/>
+      <c r="T319" s="5"/>
     </row>
     <row r="320">
-      <c r="T320" s="4"/>
+      <c r="T320" s="5"/>
     </row>
     <row r="321">
-      <c r="T321" s="4"/>
+      <c r="T321" s="5"/>
     </row>
     <row r="322">
-      <c r="T322" s="4"/>
+      <c r="T322" s="5"/>
     </row>
     <row r="323">
-      <c r="T323" s="4"/>
+      <c r="T323" s="5"/>
     </row>
     <row r="324">
-      <c r="T324" s="4"/>
+      <c r="T324" s="5"/>
     </row>
     <row r="325">
-      <c r="T325" s="4"/>
+      <c r="T325" s="5"/>
     </row>
     <row r="326">
-      <c r="T326" s="4"/>
+      <c r="T326" s="5"/>
     </row>
     <row r="327">
-      <c r="T327" s="4"/>
+      <c r="T327" s="5"/>
     </row>
     <row r="328">
-      <c r="T328" s="4"/>
+      <c r="T328" s="5"/>
     </row>
     <row r="329">
-      <c r="T329" s="4"/>
+      <c r="T329" s="5"/>
     </row>
     <row r="330">
-      <c r="T330" s="4"/>
+      <c r="T330" s="5"/>
     </row>
     <row r="331">
-      <c r="T331" s="4"/>
+      <c r="T331" s="5"/>
     </row>
     <row r="332">
-      <c r="T332" s="4"/>
+      <c r="T332" s="5"/>
     </row>
     <row r="333">
-      <c r="T333" s="4"/>
+      <c r="T333" s="5"/>
     </row>
     <row r="334">
-      <c r="T334" s="4"/>
+      <c r="T334" s="5"/>
     </row>
     <row r="335">
-      <c r="T335" s="4"/>
+      <c r="T335" s="5"/>
     </row>
     <row r="336">
-      <c r="T336" s="4"/>
+      <c r="T336" s="5"/>
     </row>
     <row r="337">
-      <c r="T337" s="4"/>
+      <c r="T337" s="5"/>
     </row>
     <row r="338">
-      <c r="T338" s="4"/>
+      <c r="T338" s="5"/>
     </row>
     <row r="339">
-      <c r="T339" s="4"/>
+      <c r="T339" s="5"/>
     </row>
     <row r="340">
-      <c r="T340" s="4"/>
+      <c r="T340" s="5"/>
     </row>
     <row r="341">
-      <c r="T341" s="4"/>
+      <c r="T341" s="5"/>
     </row>
     <row r="342">
-      <c r="T342" s="4"/>
+      <c r="T342" s="5"/>
     </row>
     <row r="343">
-      <c r="T343" s="4"/>
+      <c r="T343" s="5"/>
     </row>
     <row r="344">
-      <c r="T344" s="4"/>
+      <c r="T344" s="5"/>
     </row>
     <row r="345">
-      <c r="T345" s="4"/>
+      <c r="T345" s="5"/>
     </row>
     <row r="346">
-      <c r="T346" s="4"/>
+      <c r="T346" s="5"/>
     </row>
     <row r="347">
-      <c r="T347" s="4"/>
+      <c r="T347" s="5"/>
     </row>
     <row r="348">
-      <c r="T348" s="4"/>
+      <c r="T348" s="5"/>
     </row>
     <row r="349">
-      <c r="T349" s="4"/>
+      <c r="T349" s="5"/>
     </row>
     <row r="350">
-      <c r="T350" s="4"/>
+      <c r="T350" s="5"/>
     </row>
     <row r="351">
-      <c r="T351" s="4"/>
+      <c r="T351" s="5"/>
     </row>
     <row r="352">
-      <c r="T352" s="4"/>
+      <c r="T352" s="5"/>
     </row>
     <row r="353">
-      <c r="T353" s="4"/>
+      <c r="T353" s="5"/>
     </row>
     <row r="354">
-      <c r="T354" s="4"/>
+      <c r="T354" s="5"/>
     </row>
     <row r="355">
-      <c r="T355" s="4"/>
+      <c r="T355" s="5"/>
     </row>
     <row r="356">
-      <c r="T356" s="4"/>
+      <c r="T356" s="5"/>
     </row>
     <row r="357">
-      <c r="T357" s="4"/>
+      <c r="T357" s="5"/>
     </row>
     <row r="358">
-      <c r="T358" s="4"/>
+      <c r="T358" s="5"/>
     </row>
     <row r="359">
-      <c r="T359" s="4"/>
+      <c r="T359" s="5"/>
     </row>
     <row r="360">
-      <c r="T360" s="4"/>
+      <c r="T360" s="5"/>
     </row>
     <row r="361">
-      <c r="T361" s="4"/>
+      <c r="T361" s="5"/>
     </row>
     <row r="362">
-      <c r="T362" s="4"/>
+      <c r="T362" s="5"/>
     </row>
     <row r="363">
-      <c r="T363" s="4"/>
+      <c r="T363" s="5"/>
     </row>
     <row r="364">
-      <c r="T364" s="4"/>
+      <c r="T364" s="5"/>
     </row>
     <row r="365">
-      <c r="T365" s="4"/>
+      <c r="T365" s="5"/>
     </row>
     <row r="366">
-      <c r="T366" s="4"/>
+      <c r="T366" s="5"/>
     </row>
     <row r="367">
-      <c r="T367" s="4"/>
+      <c r="T367" s="5"/>
     </row>
     <row r="368">
-      <c r="T368" s="4"/>
+      <c r="T368" s="5"/>
     </row>
     <row r="369">
-      <c r="T369" s="4"/>
+      <c r="T369" s="5"/>
     </row>
     <row r="370">
-      <c r="T370" s="4"/>
+      <c r="T370" s="5"/>
     </row>
     <row r="371">
-      <c r="T371" s="4"/>
+      <c r="T371" s="5"/>
     </row>
     <row r="372">
-      <c r="T372" s="4"/>
+      <c r="T372" s="5"/>
     </row>
     <row r="373">
-      <c r="T373" s="4"/>
+      <c r="T373" s="5"/>
     </row>
     <row r="374">
-      <c r="T374" s="4"/>
+      <c r="T374" s="5"/>
     </row>
     <row r="375">
-      <c r="T375" s="4"/>
+      <c r="T375" s="5"/>
     </row>
     <row r="376">
-      <c r="T376" s="4"/>
+      <c r="T376" s="5"/>
     </row>
     <row r="377">
-      <c r="T377" s="4"/>
+      <c r="T377" s="5"/>
     </row>
     <row r="378">
-      <c r="T378" s="4"/>
+      <c r="T378" s="5"/>
     </row>
     <row r="379">
-      <c r="T379" s="4"/>
+      <c r="T379" s="5"/>
     </row>
     <row r="380">
-      <c r="T380" s="4"/>
+      <c r="T380" s="5"/>
     </row>
     <row r="381">
-      <c r="T381" s="4"/>
+      <c r="T381" s="5"/>
     </row>
     <row r="382">
-      <c r="T382" s="4"/>
+      <c r="T382" s="5"/>
     </row>
     <row r="383">
-      <c r="T383" s="4"/>
+      <c r="T383" s="5"/>
     </row>
     <row r="384">
-      <c r="T384" s="4"/>
+      <c r="T384" s="5"/>
     </row>
     <row r="385">
-      <c r="T385" s="4"/>
+      <c r="T385" s="5"/>
     </row>
     <row r="386">
-      <c r="T386" s="4"/>
+      <c r="T386" s="5"/>
     </row>
     <row r="387">
-      <c r="T387" s="4"/>
+      <c r="T387" s="5"/>
     </row>
     <row r="388">
-      <c r="T388" s="4"/>
+      <c r="T388" s="5"/>
     </row>
     <row r="389">
-      <c r="T389" s="4"/>
+      <c r="T389" s="5"/>
     </row>
     <row r="390">
-      <c r="T390" s="4"/>
+      <c r="T390" s="5"/>
     </row>
     <row r="391">
-      <c r="T391" s="4"/>
+      <c r="T391" s="5"/>
     </row>
     <row r="392">
-      <c r="T392" s="4"/>
+      <c r="T392" s="5"/>
     </row>
     <row r="393">
-      <c r="T393" s="4"/>
+      <c r="T393" s="5"/>
     </row>
     <row r="394">
-      <c r="T394" s="4"/>
+      <c r="T394" s="5"/>
     </row>
     <row r="395">
-      <c r="T395" s="4"/>
+      <c r="T395" s="5"/>
     </row>
     <row r="396">
-      <c r="T396" s="4"/>
+      <c r="T396" s="5"/>
     </row>
     <row r="397">
-      <c r="T397" s="4"/>
+      <c r="T397" s="5"/>
     </row>
     <row r="398">
-      <c r="T398" s="4"/>
+      <c r="T398" s="5"/>
     </row>
     <row r="399">
-      <c r="T399" s="4"/>
+      <c r="T399" s="5"/>
     </row>
     <row r="400">
-      <c r="T400" s="4"/>
+      <c r="T400" s="5"/>
     </row>
     <row r="401">
-      <c r="T401" s="4"/>
+      <c r="T401" s="5"/>
     </row>
     <row r="402">
-      <c r="T402" s="4"/>
+      <c r="T402" s="5"/>
     </row>
     <row r="403">
-      <c r="T403" s="4"/>
+      <c r="T403" s="5"/>
     </row>
     <row r="404">
-      <c r="T404" s="4"/>
+      <c r="T404" s="5"/>
     </row>
     <row r="405">
-      <c r="T405" s="4"/>
+      <c r="T405" s="5"/>
     </row>
     <row r="406">
-      <c r="T406" s="4"/>
+      <c r="T406" s="5"/>
     </row>
     <row r="407">
-      <c r="T407" s="4"/>
+      <c r="T407" s="5"/>
     </row>
     <row r="408">
-      <c r="T408" s="4"/>
+      <c r="T408" s="5"/>
     </row>
     <row r="409">
-      <c r="T409" s="4"/>
+      <c r="T409" s="5"/>
     </row>
     <row r="410">
-      <c r="T410" s="4"/>
+      <c r="T410" s="5"/>
     </row>
     <row r="411">
-      <c r="T411" s="4"/>
+      <c r="T411" s="5"/>
     </row>
     <row r="412">
-      <c r="T412" s="4"/>
+      <c r="T412" s="5"/>
     </row>
     <row r="413">
-      <c r="T413" s="4"/>
+      <c r="T413" s="5"/>
     </row>
     <row r="414">
-      <c r="T414" s="4"/>
+      <c r="T414" s="5"/>
     </row>
     <row r="415">
-      <c r="T415" s="4"/>
+      <c r="T415" s="5"/>
     </row>
     <row r="416">
-      <c r="T416" s="4"/>
+      <c r="T416" s="5"/>
     </row>
     <row r="417">
-      <c r="T417" s="4"/>
+      <c r="T417" s="5"/>
     </row>
     <row r="418">
-      <c r="T418" s="4"/>
+      <c r="T418" s="5"/>
     </row>
     <row r="419">
-      <c r="T419" s="4"/>
+      <c r="T419" s="5"/>
     </row>
     <row r="420">
-      <c r="T420" s="4"/>
+      <c r="T420" s="5"/>
     </row>
     <row r="421">
-      <c r="T421" s="4"/>
+      <c r="T421" s="5"/>
     </row>
     <row r="422">
-      <c r="T422" s="4"/>
+      <c r="T422" s="5"/>
     </row>
     <row r="423">
-      <c r="T423" s="4"/>
+      <c r="T423" s="5"/>
     </row>
     <row r="424">
-      <c r="T424" s="4"/>
+      <c r="T424" s="5"/>
     </row>
     <row r="425">
-      <c r="T425" s="4"/>
+      <c r="T425" s="5"/>
     </row>
     <row r="426">
-      <c r="T426" s="4"/>
+      <c r="T426" s="5"/>
     </row>
     <row r="427">
-      <c r="T427" s="4"/>
+      <c r="T427" s="5"/>
     </row>
     <row r="428">
-      <c r="T428" s="4"/>
+      <c r="T428" s="5"/>
     </row>
     <row r="429">
-      <c r="T429" s="4"/>
+      <c r="T429" s="5"/>
     </row>
     <row r="430">
-      <c r="T430" s="4"/>
+      <c r="T430" s="5"/>
     </row>
     <row r="431">
-      <c r="T431" s="4"/>
+      <c r="T431" s="5"/>
     </row>
     <row r="432">
-      <c r="T432" s="4"/>
+      <c r="T432" s="5"/>
     </row>
     <row r="433">
-      <c r="T433" s="4"/>
+      <c r="T433" s="5"/>
     </row>
     <row r="434">
-      <c r="T434" s="4"/>
+      <c r="T434" s="5"/>
     </row>
     <row r="435">
-      <c r="T435" s="4"/>
+      <c r="T435" s="5"/>
     </row>
     <row r="436">
-      <c r="T436" s="4"/>
+      <c r="T436" s="5"/>
     </row>
     <row r="437">
-      <c r="T437" s="4"/>
+      <c r="T437" s="5"/>
     </row>
     <row r="438">
-      <c r="T438" s="4"/>
+      <c r="T438" s="5"/>
     </row>
     <row r="439">
-      <c r="T439" s="4"/>
+      <c r="T439" s="5"/>
     </row>
     <row r="440">
-      <c r="T440" s="4"/>
+      <c r="T440" s="5"/>
     </row>
     <row r="441">
-      <c r="T441" s="4"/>
+      <c r="T441" s="5"/>
     </row>
     <row r="442">
-      <c r="T442" s="4"/>
+      <c r="T442" s="5"/>
     </row>
     <row r="443">
-      <c r="T443" s="4"/>
+      <c r="T443" s="5"/>
     </row>
     <row r="444">
-      <c r="T444" s="4"/>
+      <c r="T444" s="5"/>
     </row>
     <row r="445">
-      <c r="T445" s="4"/>
+      <c r="T445" s="5"/>
     </row>
     <row r="446">
-      <c r="T446" s="4"/>
+      <c r="T446" s="5"/>
     </row>
     <row r="447">
-      <c r="T447" s="4"/>
+      <c r="T447" s="5"/>
     </row>
     <row r="448">
-      <c r="T448" s="4"/>
+      <c r="T448" s="5"/>
     </row>
     <row r="449">
-      <c r="T449" s="4"/>
+      <c r="T449" s="5"/>
     </row>
     <row r="450">
-      <c r="T450" s="4"/>
+      <c r="T450" s="5"/>
     </row>
     <row r="451">
-      <c r="T451" s="4"/>
+      <c r="T451" s="5"/>
     </row>
     <row r="452">
-      <c r="T452" s="4"/>
+      <c r="T452" s="5"/>
     </row>
     <row r="453">
-      <c r="T453" s="4"/>
+      <c r="T453" s="5"/>
     </row>
     <row r="454">
-      <c r="T454" s="4"/>
+      <c r="T454" s="5"/>
     </row>
     <row r="455">
-      <c r="T455" s="4"/>
+      <c r="T455" s="5"/>
     </row>
     <row r="456">
-      <c r="T456" s="4"/>
+      <c r="T456" s="5"/>
     </row>
     <row r="457">
-      <c r="T457" s="4"/>
+      <c r="T457" s="5"/>
     </row>
     <row r="458">
-      <c r="T458" s="4"/>
+      <c r="T458" s="5"/>
     </row>
     <row r="459">
-      <c r="T459" s="4"/>
+      <c r="T459" s="5"/>
     </row>
     <row r="460">
-      <c r="T460" s="4"/>
+      <c r="T460" s="5"/>
     </row>
     <row r="461">
-      <c r="T461" s="4"/>
+      <c r="T461" s="5"/>
     </row>
     <row r="462">
-      <c r="T462" s="4"/>
+      <c r="T462" s="5"/>
     </row>
     <row r="463">
-      <c r="T463" s="4"/>
+      <c r="T463" s="5"/>
     </row>
     <row r="464">
-      <c r="T464" s="4"/>
+      <c r="T464" s="5"/>
     </row>
     <row r="465">
-      <c r="T465" s="4"/>
+      <c r="T465" s="5"/>
     </row>
     <row r="466">
-      <c r="T466" s="4"/>
+      <c r="T466" s="5"/>
     </row>
     <row r="467">
-      <c r="T467" s="4"/>
+      <c r="T467" s="5"/>
     </row>
     <row r="468">
-      <c r="T468" s="4"/>
+      <c r="T468" s="5"/>
     </row>
     <row r="469">
-      <c r="T469" s="4"/>
+      <c r="T469" s="5"/>
     </row>
     <row r="470">
-      <c r="T470" s="4"/>
+      <c r="T470" s="5"/>
     </row>
     <row r="471">
-      <c r="T471" s="4"/>
+      <c r="T471" s="5"/>
     </row>
     <row r="472">
-      <c r="T472" s="4"/>
+      <c r="T472" s="5"/>
     </row>
     <row r="473">
-      <c r="T473" s="4"/>
+      <c r="T473" s="5"/>
     </row>
     <row r="474">
-      <c r="T474" s="4"/>
+      <c r="T474" s="5"/>
     </row>
     <row r="475">
-      <c r="T475" s="4"/>
+      <c r="T475" s="5"/>
     </row>
     <row r="476">
-      <c r="T476" s="4"/>
+      <c r="T476" s="5"/>
     </row>
     <row r="477">
-      <c r="T477" s="4"/>
+      <c r="T477" s="5"/>
     </row>
     <row r="478">
-      <c r="T478" s="4"/>
+      <c r="T478" s="5"/>
     </row>
     <row r="479">
-      <c r="T479" s="4"/>
+      <c r="T479" s="5"/>
     </row>
     <row r="480">
-      <c r="T480" s="4"/>
+      <c r="T480" s="5"/>
     </row>
     <row r="481">
-      <c r="T481" s="4"/>
+      <c r="T481" s="5"/>
     </row>
     <row r="482">
-      <c r="T482" s="4"/>
+      <c r="T482" s="5"/>
     </row>
     <row r="483">
-      <c r="T483" s="4"/>
+      <c r="T483" s="5"/>
     </row>
     <row r="484">
-      <c r="T484" s="4"/>
+      <c r="T484" s="5"/>
     </row>
     <row r="485">
-      <c r="T485" s="4"/>
+      <c r="T485" s="5"/>
     </row>
     <row r="486">
-      <c r="T486" s="4"/>
+      <c r="T486" s="5"/>
     </row>
     <row r="487">
-      <c r="T487" s="4"/>
+      <c r="T487" s="5"/>
     </row>
     <row r="488">
-      <c r="T488" s="4"/>
+      <c r="T488" s="5"/>
     </row>
     <row r="489">
-      <c r="T489" s="4"/>
+      <c r="T489" s="5"/>
     </row>
     <row r="490">
-      <c r="T490" s="4"/>
+      <c r="T490" s="5"/>
     </row>
     <row r="491">
-      <c r="T491" s="4"/>
+      <c r="T491" s="5"/>
     </row>
     <row r="492">
-      <c r="T492" s="4"/>
+      <c r="T492" s="5"/>
     </row>
     <row r="493">
-      <c r="T493" s="4"/>
+      <c r="T493" s="5"/>
     </row>
     <row r="494">
-      <c r="T494" s="4"/>
+      <c r="T494" s="5"/>
     </row>
     <row r="495">
-      <c r="T495" s="4"/>
+      <c r="T495" s="5"/>
     </row>
     <row r="496">
-      <c r="T496" s="4"/>
+      <c r="T496" s="5"/>
     </row>
     <row r="497">
-      <c r="T497" s="4"/>
+      <c r="T497" s="5"/>
     </row>
     <row r="498">
-      <c r="T498" s="4"/>
+      <c r="T498" s="5"/>
     </row>
     <row r="499">
-      <c r="T499" s="4"/>
+      <c r="T499" s="5"/>
     </row>
     <row r="500">
-      <c r="T500" s="4"/>
+      <c r="T500" s="5"/>
     </row>
     <row r="501">
-      <c r="T501" s="4"/>
+      <c r="T501" s="5"/>
     </row>
     <row r="502">
-      <c r="T502" s="4"/>
+      <c r="T502" s="5"/>
     </row>
     <row r="503">
-      <c r="T503" s="4"/>
+      <c r="T503" s="5"/>
     </row>
     <row r="504">
-      <c r="T504" s="4"/>
+      <c r="T504" s="5"/>
     </row>
     <row r="505">
-      <c r="T505" s="4"/>
+      <c r="T505" s="5"/>
     </row>
     <row r="506">
-      <c r="T506" s="4"/>
+      <c r="T506" s="5"/>
     </row>
     <row r="507">
-      <c r="T507" s="4"/>
+      <c r="T507" s="5"/>
     </row>
     <row r="508">
-      <c r="T508" s="4"/>
+      <c r="T508" s="5"/>
     </row>
     <row r="509">
-      <c r="T509" s="4"/>
+      <c r="T509" s="5"/>
     </row>
     <row r="510">
-      <c r="T510" s="4"/>
+      <c r="T510" s="5"/>
     </row>
     <row r="511">
-      <c r="T511" s="4"/>
+      <c r="T511" s="5"/>
     </row>
     <row r="512">
-      <c r="T512" s="4"/>
+      <c r="T512" s="5"/>
     </row>
     <row r="513">
-      <c r="T513" s="4"/>
+      <c r="T513" s="5"/>
     </row>
     <row r="514">
-      <c r="T514" s="4"/>
+      <c r="T514" s="5"/>
     </row>
     <row r="515">
-      <c r="T515" s="4"/>
+      <c r="T515" s="5"/>
     </row>
     <row r="516">
-      <c r="T516" s="4"/>
+      <c r="T516" s="5"/>
     </row>
     <row r="517">
-      <c r="T517" s="4"/>
+      <c r="T517" s="5"/>
     </row>
     <row r="518">
-      <c r="T518" s="4"/>
+      <c r="T518" s="5"/>
     </row>
     <row r="519">
-      <c r="T519" s="4"/>
+      <c r="T519" s="5"/>
     </row>
     <row r="520">
-      <c r="T520" s="4"/>
+      <c r="T520" s="5"/>
     </row>
     <row r="521">
-      <c r="T521" s="4"/>
+      <c r="T521" s="5"/>
     </row>
     <row r="522">
-      <c r="T522" s="4"/>
+      <c r="T522" s="5"/>
     </row>
     <row r="523">
-      <c r="T523" s="4"/>
+      <c r="T523" s="5"/>
     </row>
     <row r="524">
-      <c r="T524" s="4"/>
+      <c r="T524" s="5"/>
     </row>
     <row r="525">
-      <c r="T525" s="4"/>
+      <c r="T525" s="5"/>
     </row>
     <row r="526">
-      <c r="T526" s="4"/>
+      <c r="T526" s="5"/>
     </row>
     <row r="527">
-      <c r="T527" s="4"/>
+      <c r="T527" s="5"/>
     </row>
     <row r="528">
-      <c r="T528" s="4"/>
+      <c r="T528" s="5"/>
     </row>
     <row r="529">
-      <c r="T529" s="4"/>
+      <c r="T529" s="5"/>
     </row>
     <row r="530">
-      <c r="T530" s="4"/>
+      <c r="T530" s="5"/>
     </row>
     <row r="531">
-      <c r="T531" s="4"/>
+      <c r="T531" s="5"/>
     </row>
     <row r="532">
-      <c r="T532" s="4"/>
+      <c r="T532" s="5"/>
     </row>
     <row r="533">
-      <c r="T533" s="4"/>
+      <c r="T533" s="5"/>
     </row>
     <row r="534">
-      <c r="T534" s="4"/>
+      <c r="T534" s="5"/>
     </row>
     <row r="535">
-      <c r="T535" s="4"/>
+      <c r="T535" s="5"/>
     </row>
     <row r="536">
-      <c r="T536" s="4"/>
+      <c r="T536" s="5"/>
     </row>
     <row r="537">
-      <c r="T537" s="4"/>
+      <c r="T537" s="5"/>
     </row>
     <row r="538">
-      <c r="T538" s="4"/>
+      <c r="T538" s="5"/>
     </row>
     <row r="539">
-      <c r="T539" s="4"/>
+      <c r="T539" s="5"/>
     </row>
     <row r="540">
-      <c r="T540" s="4"/>
+      <c r="T540" s="5"/>
     </row>
     <row r="541">
-      <c r="T541" s="4"/>
+      <c r="T541" s="5"/>
     </row>
     <row r="542">
-      <c r="T542" s="4"/>
+      <c r="T542" s="5"/>
     </row>
     <row r="543">
-      <c r="T543" s="4"/>
+      <c r="T543" s="5"/>
     </row>
     <row r="544">
-      <c r="T544" s="4"/>
+      <c r="T544" s="5"/>
     </row>
     <row r="545">
-      <c r="T545" s="4"/>
+      <c r="T545" s="5"/>
     </row>
     <row r="546">
-      <c r="T546" s="4"/>
+      <c r="T546" s="5"/>
     </row>
     <row r="547">
-      <c r="T547" s="4"/>
+      <c r="T547" s="5"/>
     </row>
     <row r="548">
-      <c r="T548" s="4"/>
+      <c r="T548" s="5"/>
     </row>
     <row r="549">
-      <c r="T549" s="4"/>
+      <c r="T549" s="5"/>
     </row>
     <row r="550">
-      <c r="T550" s="4"/>
+      <c r="T550" s="5"/>
     </row>
     <row r="551">
-      <c r="T551" s="4"/>
+      <c r="T551" s="5"/>
     </row>
     <row r="552">
-      <c r="T552" s="4"/>
+      <c r="T552" s="5"/>
     </row>
     <row r="553">
-      <c r="T553" s="4"/>
+      <c r="T553" s="5"/>
     </row>
     <row r="554">
-      <c r="T554" s="4"/>
+      <c r="T554" s="5"/>
     </row>
     <row r="555">
-      <c r="T555" s="4"/>
+      <c r="T555" s="5"/>
     </row>
     <row r="556">
-      <c r="T556" s="4"/>
+      <c r="T556" s="5"/>
     </row>
     <row r="557">
-      <c r="T557" s="4"/>
+      <c r="T557" s="5"/>
     </row>
     <row r="558">
-      <c r="T558" s="4"/>
+      <c r="T558" s="5"/>
     </row>
     <row r="559">
-      <c r="T559" s="4"/>
+      <c r="T559" s="5"/>
     </row>
     <row r="560">
-      <c r="T560" s="4"/>
+      <c r="T560" s="5"/>
     </row>
     <row r="561">
-      <c r="T561" s="4"/>
+      <c r="T561" s="5"/>
     </row>
     <row r="562">
-      <c r="T562" s="4"/>
+      <c r="T562" s="5"/>
     </row>
     <row r="563">
-      <c r="T563" s="4"/>
+      <c r="T563" s="5"/>
     </row>
     <row r="564">
-      <c r="T564" s="4"/>
+      <c r="T564" s="5"/>
     </row>
     <row r="565">
-      <c r="T565" s="4"/>
+      <c r="T565" s="5"/>
     </row>
     <row r="566">
-      <c r="T566" s="4"/>
+      <c r="T566" s="5"/>
     </row>
     <row r="567">
-      <c r="T567" s="4"/>
+      <c r="T567" s="5"/>
     </row>
     <row r="568">
-      <c r="T568" s="4"/>
+      <c r="T568" s="5"/>
     </row>
     <row r="569">
-      <c r="T569" s="4"/>
+      <c r="T569" s="5"/>
     </row>
     <row r="570">
-      <c r="T570" s="4"/>
+      <c r="T570" s="5"/>
     </row>
     <row r="571">
-      <c r="T571" s="4"/>
+      <c r="T571" s="5"/>
     </row>
     <row r="572">
-      <c r="T572" s="4"/>
+      <c r="T572" s="5"/>
     </row>
     <row r="573">
-      <c r="T573" s="4"/>
+      <c r="T573" s="5"/>
     </row>
     <row r="574">
-      <c r="T574" s="4"/>
+      <c r="T574" s="5"/>
     </row>
     <row r="575">
-      <c r="T575" s="4"/>
+      <c r="T575" s="5"/>
     </row>
     <row r="576">
-      <c r="T576" s="4"/>
+      <c r="T576" s="5"/>
     </row>
     <row r="577">
-      <c r="T577" s="4"/>
+      <c r="T577" s="5"/>
     </row>
     <row r="578">
-      <c r="T578" s="4"/>
+      <c r="T578" s="5"/>
     </row>
     <row r="579">
-      <c r="T579" s="4"/>
+      <c r="T579" s="5"/>
     </row>
     <row r="580">
-      <c r="T580" s="4"/>
+      <c r="T580" s="5"/>
     </row>
     <row r="581">
-      <c r="T581" s="4"/>
+      <c r="T581" s="5"/>
     </row>
     <row r="582">
-      <c r="T582" s="4"/>
+      <c r="T582" s="5"/>
     </row>
     <row r="583">
-      <c r="T583" s="4"/>
+      <c r="T583" s="5"/>
     </row>
     <row r="584">
-      <c r="T584" s="4"/>
+      <c r="T584" s="5"/>
     </row>
     <row r="585">
-      <c r="T585" s="4"/>
+      <c r="T585" s="5"/>
     </row>
     <row r="586">
-      <c r="T586" s="4"/>
+      <c r="T586" s="5"/>
     </row>
     <row r="587">
-      <c r="T587" s="4"/>
+      <c r="T587" s="5"/>
     </row>
     <row r="588">
-      <c r="T588" s="4"/>
+      <c r="T588" s="5"/>
     </row>
     <row r="589">
-      <c r="T589" s="4"/>
+      <c r="T589" s="5"/>
     </row>
     <row r="590">
-      <c r="T590" s="4"/>
+      <c r="T590" s="5"/>
     </row>
     <row r="591">
-      <c r="T591" s="4"/>
+      <c r="T591" s="5"/>
     </row>
     <row r="592">
-      <c r="T592" s="4"/>
+      <c r="T592" s="5"/>
     </row>
     <row r="593">
-      <c r="T593" s="4"/>
+      <c r="T593" s="5"/>
     </row>
     <row r="594">
-      <c r="T594" s="4"/>
+      <c r="T594" s="5"/>
     </row>
     <row r="595">
-      <c r="T595" s="4"/>
+      <c r="T595" s="5"/>
     </row>
     <row r="596">
-      <c r="T596" s="4"/>
+      <c r="T596" s="5"/>
     </row>
     <row r="597">
-      <c r="T597" s="4"/>
+      <c r="T597" s="5"/>
     </row>
     <row r="598">
-      <c r="T598" s="4"/>
+      <c r="T598" s="5"/>
     </row>
     <row r="599">
-      <c r="T599" s="4"/>
+      <c r="T599" s="5"/>
     </row>
     <row r="600">
-      <c r="T600" s="4"/>
+      <c r="T600" s="5"/>
     </row>
     <row r="601">
-      <c r="T601" s="4"/>
+      <c r="T601" s="5"/>
     </row>
     <row r="602">
-      <c r="T602" s="4"/>
+      <c r="T602" s="5"/>
     </row>
     <row r="603">
-      <c r="T603" s="4"/>
+      <c r="T603" s="5"/>
     </row>
     <row r="604">
-      <c r="T604" s="4"/>
+      <c r="T604" s="5"/>
     </row>
     <row r="605">
-      <c r="T605" s="4"/>
+      <c r="T605" s="5"/>
     </row>
     <row r="606">
-      <c r="T606" s="4"/>
+      <c r="T606" s="5"/>
     </row>
     <row r="607">
-      <c r="T607" s="4"/>
+      <c r="T607" s="5"/>
     </row>
     <row r="608">
-      <c r="T608" s="4"/>
+      <c r="T608" s="5"/>
     </row>
     <row r="609">
-      <c r="T609" s="4"/>
+      <c r="T609" s="5"/>
     </row>
     <row r="610">
-      <c r="T610" s="4"/>
+      <c r="T610" s="5"/>
     </row>
     <row r="611">
-      <c r="T611" s="4"/>
+      <c r="T611" s="5"/>
     </row>
     <row r="612">
-      <c r="T612" s="4"/>
+      <c r="T612" s="5"/>
     </row>
     <row r="613">
-      <c r="T613" s="4"/>
+      <c r="T613" s="5"/>
     </row>
     <row r="614">
-      <c r="T614" s="4"/>
+      <c r="T614" s="5"/>
     </row>
     <row r="615">
-      <c r="T615" s="4"/>
+      <c r="T615" s="5"/>
     </row>
     <row r="616">
-      <c r="T616" s="4"/>
+      <c r="T616" s="5"/>
     </row>
     <row r="617">
-      <c r="T617" s="4"/>
+      <c r="T617" s="5"/>
     </row>
     <row r="618">
-      <c r="T618" s="4"/>
+      <c r="T618" s="5"/>
     </row>
     <row r="619">
-      <c r="T619" s="4"/>
+      <c r="T619" s="5"/>
     </row>
     <row r="620">
-      <c r="T620" s="4"/>
+      <c r="T620" s="5"/>
     </row>
     <row r="621">
-      <c r="T621" s="4"/>
+      <c r="T621" s="5"/>
     </row>
     <row r="622">
-      <c r="T622" s="4"/>
+      <c r="T622" s="5"/>
     </row>
     <row r="623">
-      <c r="T623" s="4"/>
+      <c r="T623" s="5"/>
     </row>
     <row r="624">
-      <c r="T624" s="4"/>
+      <c r="T624" s="5"/>
     </row>
     <row r="625">
-      <c r="T625" s="4"/>
+      <c r="T625" s="5"/>
     </row>
     <row r="626">
-      <c r="T626" s="4"/>
+      <c r="T626" s="5"/>
     </row>
     <row r="627">
-      <c r="T627" s="4"/>
+      <c r="T627" s="5"/>
     </row>
     <row r="628">
-      <c r="T628" s="4"/>
+      <c r="T628" s="5"/>
     </row>
     <row r="629">
-      <c r="T629" s="4"/>
+      <c r="T629" s="5"/>
     </row>
     <row r="630">
-      <c r="T630" s="4"/>
+      <c r="T630" s="5"/>
     </row>
     <row r="631">
-      <c r="T631" s="4"/>
+      <c r="T631" s="5"/>
     </row>
     <row r="632">
-      <c r="T632" s="4"/>
+      <c r="T632" s="5"/>
     </row>
     <row r="633">
-      <c r="T633" s="4"/>
+      <c r="T633" s="5"/>
     </row>
     <row r="634">
-      <c r="T634" s="4"/>
+      <c r="T634" s="5"/>
     </row>
     <row r="635">
-      <c r="T635" s="4"/>
+      <c r="T635" s="5"/>
     </row>
     <row r="636">
-      <c r="T636" s="4"/>
+      <c r="T636" s="5"/>
     </row>
     <row r="637">
-      <c r="T637" s="4"/>
+      <c r="T637" s="5"/>
     </row>
     <row r="638">
-      <c r="T638" s="4"/>
+      <c r="T638" s="5"/>
     </row>
     <row r="639">
-      <c r="T639" s="4"/>
+      <c r="T639" s="5"/>
     </row>
     <row r="640">
-      <c r="T640" s="4"/>
+      <c r="T640" s="5"/>
     </row>
     <row r="641">
-      <c r="T641" s="4"/>
+      <c r="T641" s="5"/>
     </row>
     <row r="642">
-      <c r="T642" s="4"/>
+      <c r="T642" s="5"/>
     </row>
     <row r="643">
-      <c r="T643" s="4"/>
+      <c r="T643" s="5"/>
     </row>
     <row r="644">
-      <c r="T644" s="4"/>
+      <c r="T644" s="5"/>
     </row>
     <row r="645">
-      <c r="T645" s="4"/>
+      <c r="T645" s="5"/>
     </row>
     <row r="646">
-      <c r="T646" s="4"/>
+      <c r="T646" s="5"/>
     </row>
     <row r="647">
-      <c r="T647" s="4"/>
+      <c r="T647" s="5"/>
     </row>
     <row r="648">
-      <c r="T648" s="4"/>
+      <c r="T648" s="5"/>
     </row>
     <row r="649">
-      <c r="T649" s="4"/>
+      <c r="T649" s="5"/>
     </row>
     <row r="650">
-      <c r="T650" s="4"/>
+      <c r="T650" s="5"/>
     </row>
     <row r="651">
-      <c r="T651" s="4"/>
+      <c r="T651" s="5"/>
     </row>
     <row r="652">
-      <c r="T652" s="4"/>
+      <c r="T652" s="5"/>
     </row>
     <row r="653">
-      <c r="T653" s="4"/>
+      <c r="T653" s="5"/>
     </row>
     <row r="654">
-      <c r="T654" s="4"/>
+      <c r="T654" s="5"/>
     </row>
     <row r="655">
-      <c r="T655" s="4"/>
+      <c r="T655" s="5"/>
     </row>
     <row r="656">
-      <c r="T656" s="4"/>
+      <c r="T656" s="5"/>
     </row>
     <row r="657">
-      <c r="T657" s="4"/>
+      <c r="T657" s="5"/>
     </row>
     <row r="658">
-      <c r="T658" s="4"/>
+      <c r="T658" s="5"/>
     </row>
     <row r="659">
-      <c r="T659" s="4"/>
+      <c r="T659" s="5"/>
     </row>
     <row r="660">
-      <c r="T660" s="4"/>
+      <c r="T660" s="5"/>
     </row>
     <row r="661">
-      <c r="T661" s="4"/>
+      <c r="T661" s="5"/>
     </row>
     <row r="662">
-      <c r="T662" s="4"/>
+      <c r="T662" s="5"/>
     </row>
     <row r="663">
-      <c r="T663" s="4"/>
+      <c r="T663" s="5"/>
     </row>
     <row r="664">
-      <c r="T664" s="4"/>
+      <c r="T664" s="5"/>
     </row>
     <row r="665">
-      <c r="T665" s="4"/>
+      <c r="T665" s="5"/>
     </row>
     <row r="666">
-      <c r="T666" s="4"/>
+      <c r="T666" s="5"/>
     </row>
     <row r="667">
-      <c r="T667" s="4"/>
+      <c r="T667" s="5"/>
     </row>
     <row r="668">
-      <c r="T668" s="4"/>
+      <c r="T668" s="5"/>
     </row>
     <row r="669">
-      <c r="T669" s="4"/>
+      <c r="T669" s="5"/>
     </row>
     <row r="670">
-      <c r="T670" s="4"/>
+      <c r="T670" s="5"/>
     </row>
     <row r="671">
-      <c r="T671" s="4"/>
+      <c r="T671" s="5"/>
     </row>
     <row r="672">
-      <c r="T672" s="4"/>
+      <c r="T672" s="5"/>
     </row>
     <row r="673">
-      <c r="T673" s="4"/>
+      <c r="T673" s="5"/>
     </row>
     <row r="674">
-      <c r="T674" s="4"/>
+      <c r="T674" s="5"/>
     </row>
     <row r="675">
-      <c r="T675" s="4"/>
+      <c r="T675" s="5"/>
     </row>
     <row r="676">
-      <c r="T676" s="4"/>
+      <c r="T676" s="5"/>
     </row>
     <row r="677">
-      <c r="T677" s="4"/>
+      <c r="T677" s="5"/>
     </row>
     <row r="678">
-      <c r="T678" s="4"/>
+      <c r="T678" s="5"/>
     </row>
     <row r="679">
-      <c r="T679" s="4"/>
+      <c r="T679" s="5"/>
     </row>
     <row r="680">
-      <c r="T680" s="4"/>
+      <c r="T680" s="5"/>
     </row>
     <row r="681">
-      <c r="T681" s="4"/>
+      <c r="T681" s="5"/>
     </row>
     <row r="682">
-      <c r="T682" s="4"/>
+      <c r="T682" s="5"/>
     </row>
     <row r="683">
-      <c r="T683" s="4"/>
+      <c r="T683" s="5"/>
     </row>
     <row r="684">
-      <c r="T684" s="4"/>
+      <c r="T684" s="5"/>
     </row>
     <row r="685">
-      <c r="T685" s="4"/>
+      <c r="T685" s="5"/>
     </row>
     <row r="686">
-      <c r="T686" s="4"/>
+      <c r="T686" s="5"/>
     </row>
     <row r="687">
-      <c r="T687" s="4"/>
+      <c r="T687" s="5"/>
     </row>
     <row r="688">
-      <c r="T688" s="4"/>
+      <c r="T688" s="5"/>
     </row>
     <row r="689">
-      <c r="T689" s="4"/>
+      <c r="T689" s="5"/>
     </row>
     <row r="690">
-      <c r="T690" s="4"/>
+      <c r="T690" s="5"/>
     </row>
     <row r="691">
-      <c r="T691" s="4"/>
+      <c r="T691" s="5"/>
     </row>
     <row r="692">
-      <c r="T692" s="4"/>
+      <c r="T692" s="5"/>
     </row>
     <row r="693">
-      <c r="T693" s="4"/>
+      <c r="T693" s="5"/>
     </row>
     <row r="694">
-      <c r="T694" s="4"/>
+      <c r="T694" s="5"/>
     </row>
     <row r="695">
-      <c r="T695" s="4"/>
+      <c r="T695" s="5"/>
     </row>
     <row r="696">
-      <c r="T696" s="4"/>
+      <c r="T696" s="5"/>
     </row>
     <row r="697">
-      <c r="T697" s="4"/>
+      <c r="T697" s="5"/>
     </row>
     <row r="698">
-      <c r="T698" s="4"/>
+      <c r="T698" s="5"/>
     </row>
     <row r="699">
-      <c r="T699" s="4"/>
+      <c r="T699" s="5"/>
     </row>
     <row r="700">
-      <c r="T700" s="4"/>
+      <c r="T700" s="5"/>
     </row>
     <row r="701">
-      <c r="T701" s="4"/>
+      <c r="T701" s="5"/>
     </row>
     <row r="702">
-      <c r="T702" s="4"/>
+      <c r="T702" s="5"/>
     </row>
     <row r="703">
-      <c r="T703" s="4"/>
+      <c r="T703" s="5"/>
     </row>
     <row r="704">
-      <c r="T704" s="4"/>
+      <c r="T704" s="5"/>
     </row>
     <row r="705">
-      <c r="T705" s="4"/>
+      <c r="T705" s="5"/>
     </row>
     <row r="706">
-      <c r="T706" s="4"/>
+      <c r="T706" s="5"/>
     </row>
     <row r="707">
-      <c r="T707" s="4"/>
+      <c r="T707" s="5"/>
     </row>
     <row r="708">
-      <c r="T708" s="4"/>
+      <c r="T708" s="5"/>
     </row>
     <row r="709">
-      <c r="T709" s="4"/>
+      <c r="T709" s="5"/>
     </row>
     <row r="710">
-      <c r="T710" s="4"/>
+      <c r="T710" s="5"/>
     </row>
     <row r="711">
-      <c r="T711" s="4"/>
+      <c r="T711" s="5"/>
     </row>
     <row r="712">
-      <c r="T712" s="4"/>
+      <c r="T712" s="5"/>
     </row>
     <row r="713">
-      <c r="T713" s="4"/>
+      <c r="T713" s="5"/>
     </row>
     <row r="714">
-      <c r="T714" s="4"/>
+      <c r="T714" s="5"/>
     </row>
     <row r="715">
-      <c r="T715" s="4"/>
+      <c r="T715" s="5"/>
     </row>
     <row r="716">
-      <c r="T716" s="4"/>
+      <c r="T716" s="5"/>
     </row>
     <row r="717">
-      <c r="T717" s="4"/>
+      <c r="T717" s="5"/>
     </row>
     <row r="718">
-      <c r="T718" s="4"/>
+      <c r="T718" s="5"/>
     </row>
     <row r="719">
-      <c r="T719" s="4"/>
+      <c r="T719" s="5"/>
     </row>
     <row r="720">
-      <c r="T720" s="4"/>
+      <c r="T720" s="5"/>
     </row>
     <row r="721">
-      <c r="T721" s="4"/>
+      <c r="T721" s="5"/>
     </row>
     <row r="722">
-      <c r="T722" s="4"/>
+      <c r="T722" s="5"/>
     </row>
     <row r="723">
-      <c r="T723" s="4"/>
+      <c r="T723" s="5"/>
     </row>
     <row r="724">
-      <c r="T724" s="4"/>
+      <c r="T724" s="5"/>
     </row>
     <row r="725">
-      <c r="T725" s="4"/>
+      <c r="T725" s="5"/>
     </row>
     <row r="726">
-      <c r="T726" s="4"/>
+      <c r="T726" s="5"/>
     </row>
     <row r="727">
-      <c r="T727" s="4"/>
+      <c r="T727" s="5"/>
     </row>
     <row r="728">
-      <c r="T728" s="4"/>
+      <c r="T728" s="5"/>
     </row>
     <row r="729">
-      <c r="T729" s="4"/>
+      <c r="T729" s="5"/>
     </row>
     <row r="730">
-      <c r="T730" s="4"/>
+      <c r="T730" s="5"/>
     </row>
     <row r="731">
-      <c r="T731" s="4"/>
+      <c r="T731" s="5"/>
     </row>
     <row r="732">
-      <c r="T732" s="4"/>
+      <c r="T732" s="5"/>
     </row>
     <row r="733">
-      <c r="T733" s="4"/>
+      <c r="T733" s="5"/>
     </row>
     <row r="734">
-      <c r="T734" s="4"/>
+      <c r="T734" s="5"/>
     </row>
     <row r="735">
-      <c r="T735" s="4"/>
+      <c r="T735" s="5"/>
     </row>
     <row r="736">
-      <c r="T736" s="4"/>
+      <c r="T736" s="5"/>
     </row>
     <row r="737">
-      <c r="T737" s="4"/>
+      <c r="T737" s="5"/>
     </row>
     <row r="738">
-      <c r="T738" s="4"/>
+      <c r="T738" s="5"/>
     </row>
     <row r="739">
-      <c r="T739" s="4"/>
+      <c r="T739" s="5"/>
     </row>
     <row r="740">
-      <c r="T740" s="4"/>
+      <c r="T740" s="5"/>
     </row>
     <row r="741">
-      <c r="T741" s="4"/>
+      <c r="T741" s="5"/>
     </row>
     <row r="742">
-      <c r="T742" s="4"/>
+      <c r="T742" s="5"/>
     </row>
     <row r="743">
-      <c r="T743" s="4"/>
+      <c r="T743" s="5"/>
     </row>
     <row r="744">
-      <c r="T744" s="4"/>
+      <c r="T744" s="5"/>
     </row>
     <row r="745">
-      <c r="T745" s="4"/>
+      <c r="T745" s="5"/>
     </row>
     <row r="746">
-      <c r="T746" s="4"/>
+      <c r="T746" s="5"/>
     </row>
     <row r="747">
-      <c r="T747" s="4"/>
+      <c r="T747" s="5"/>
     </row>
     <row r="748">
-      <c r="T748" s="4"/>
+      <c r="T748" s="5"/>
     </row>
     <row r="749">
-      <c r="T749" s="4"/>
+      <c r="T749" s="5"/>
     </row>
     <row r="750">
-      <c r="T750" s="4"/>
+      <c r="T750" s="5"/>
     </row>
     <row r="751">
-      <c r="T751" s="4"/>
+      <c r="T751" s="5"/>
     </row>
     <row r="752">
-      <c r="T752" s="4"/>
+      <c r="T752" s="5"/>
     </row>
     <row r="753">
-      <c r="T753" s="4"/>
+      <c r="T753" s="5"/>
     </row>
     <row r="754">
-      <c r="T754" s="4"/>
+      <c r="T754" s="5"/>
     </row>
     <row r="755">
-      <c r="T755" s="4"/>
+      <c r="T755" s="5"/>
     </row>
     <row r="756">
-      <c r="T756" s="4"/>
+      <c r="T756" s="5"/>
     </row>
     <row r="757">
-      <c r="T757" s="4"/>
+      <c r="T757" s="5"/>
     </row>
     <row r="758">
-      <c r="T758" s="4"/>
+      <c r="T758" s="5"/>
     </row>
     <row r="759">
-      <c r="T759" s="4"/>
+      <c r="T759" s="5"/>
     </row>
     <row r="760">
-      <c r="T760" s="4"/>
+      <c r="T760" s="5"/>
     </row>
     <row r="761">
-      <c r="T761" s="4"/>
+      <c r="T761" s="5"/>
     </row>
     <row r="762">
-      <c r="T762" s="4"/>
+      <c r="T762" s="5"/>
     </row>
     <row r="763">
-      <c r="T763" s="4"/>
+      <c r="T763" s="5"/>
     </row>
     <row r="764">
-      <c r="T764" s="4"/>
+      <c r="T764" s="5"/>
     </row>
     <row r="765">
-      <c r="T765" s="4"/>
+      <c r="T765" s="5"/>
     </row>
     <row r="766">
-      <c r="T766" s="4"/>
+      <c r="T766" s="5"/>
     </row>
     <row r="767">
-      <c r="T767" s="4"/>
+      <c r="T767" s="5"/>
     </row>
     <row r="768">
-      <c r="T768" s="4"/>
+      <c r="T768" s="5"/>
     </row>
     <row r="769">
-      <c r="T769" s="4"/>
+      <c r="T769" s="5"/>
     </row>
     <row r="770">
-      <c r="T770" s="4"/>
+      <c r="T770" s="5"/>
     </row>
     <row r="771">
-      <c r="T771" s="4"/>
+      <c r="T771" s="5"/>
     </row>
     <row r="772">
-      <c r="T772" s="4"/>
+      <c r="T772" s="5"/>
     </row>
     <row r="773">
-      <c r="T773" s="4"/>
+      <c r="T773" s="5"/>
     </row>
     <row r="774">
-      <c r="T774" s="4"/>
+      <c r="T774" s="5"/>
     </row>
     <row r="775">
-      <c r="T775" s="4"/>
+      <c r="T775" s="5"/>
     </row>
     <row r="776">
-      <c r="T776" s="4"/>
+      <c r="T776" s="5"/>
     </row>
     <row r="777">
-      <c r="T777" s="4"/>
+      <c r="T777" s="5"/>
     </row>
     <row r="778">
-      <c r="T778" s="4"/>
+      <c r="T778" s="5"/>
     </row>
     <row r="779">
-      <c r="T779" s="4"/>
+      <c r="T779" s="5"/>
     </row>
     <row r="780">
-      <c r="T780" s="4"/>
+      <c r="T780" s="5"/>
     </row>
     <row r="781">
-      <c r="T781" s="4"/>
+      <c r="T781" s="5"/>
     </row>
     <row r="782">
-      <c r="T782" s="4"/>
+      <c r="T782" s="5"/>
     </row>
     <row r="783">
-      <c r="T783" s="4"/>
+      <c r="T783" s="5"/>
     </row>
     <row r="784">
-      <c r="T784" s="4"/>
+      <c r="T784" s="5"/>
     </row>
     <row r="785">
-      <c r="T785" s="4"/>
+      <c r="T785" s="5"/>
     </row>
     <row r="786">
-      <c r="T786" s="4"/>
+      <c r="T786" s="5"/>
     </row>
     <row r="787">
-      <c r="T787" s="4"/>
+      <c r="T787" s="5"/>
     </row>
     <row r="788">
-      <c r="T788" s="4"/>
+      <c r="T788" s="5"/>
     </row>
     <row r="789">
-      <c r="T789" s="4"/>
+      <c r="T789" s="5"/>
     </row>
     <row r="790">
-      <c r="T790" s="4"/>
+      <c r="T790" s="5"/>
     </row>
     <row r="791">
-      <c r="T791" s="4"/>
+      <c r="T791" s="5"/>
     </row>
     <row r="792">
-      <c r="T792" s="4"/>
+      <c r="T792" s="5"/>
     </row>
     <row r="793">
-      <c r="T793" s="4"/>
+      <c r="T793" s="5"/>
     </row>
     <row r="794">
-      <c r="T794" s="4"/>
+      <c r="T794" s="5"/>
     </row>
     <row r="795">
-      <c r="T795" s="4"/>
+      <c r="T795" s="5"/>
     </row>
     <row r="796">
-      <c r="T796" s="4"/>
+      <c r="T796" s="5"/>
     </row>
     <row r="797">
-      <c r="T797" s="4"/>
+      <c r="T797" s="5"/>
     </row>
     <row r="798">
-      <c r="T798" s="4"/>
+      <c r="T798" s="5"/>
     </row>
     <row r="799">
-      <c r="T799" s="4"/>
+      <c r="T799" s="5"/>
     </row>
     <row r="800">
-      <c r="T800" s="4"/>
+      <c r="T800" s="5"/>
     </row>
     <row r="801">
-      <c r="T801" s="4"/>
+      <c r="T801" s="5"/>
     </row>
     <row r="802">
-      <c r="T802" s="4"/>
+      <c r="T802" s="5"/>
     </row>
     <row r="803">
-      <c r="T803" s="4"/>
+      <c r="T803" s="5"/>
     </row>
     <row r="804">
-      <c r="T804" s="4"/>
+      <c r="T804" s="5"/>
     </row>
     <row r="805">
-      <c r="T805" s="4"/>
+      <c r="T805" s="5"/>
     </row>
     <row r="806">
-      <c r="T806" s="4"/>
+      <c r="T806" s="5"/>
     </row>
     <row r="807">
-      <c r="T807" s="4"/>
+      <c r="T807" s="5"/>
     </row>
     <row r="808">
-      <c r="T808" s="4"/>
+      <c r="T808" s="5"/>
     </row>
     <row r="809">
-      <c r="T809" s="4"/>
+      <c r="T809" s="5"/>
     </row>
     <row r="810">
-      <c r="T810" s="4"/>
+      <c r="T810" s="5"/>
     </row>
     <row r="811">
-      <c r="T811" s="4"/>
+      <c r="T811" s="5"/>
     </row>
     <row r="812">
-      <c r="T812" s="4"/>
+      <c r="T812" s="5"/>
     </row>
     <row r="813">
-      <c r="T813" s="4"/>
+      <c r="T813" s="5"/>
     </row>
     <row r="814">
-      <c r="T814" s="4"/>
+      <c r="T814" s="5"/>
     </row>
     <row r="815">
-      <c r="T815" s="4"/>
+      <c r="T815" s="5"/>
     </row>
     <row r="816">
-      <c r="T816" s="4"/>
+      <c r="T816" s="5"/>
     </row>
     <row r="817">
-      <c r="T817" s="4"/>
+      <c r="T817" s="5"/>
     </row>
     <row r="818">
-      <c r="T818" s="4"/>
+      <c r="T818" s="5"/>
     </row>
     <row r="819">
-      <c r="T819" s="4"/>
+      <c r="T819" s="5"/>
     </row>
     <row r="820">
-      <c r="T820" s="4"/>
+      <c r="T820" s="5"/>
     </row>
     <row r="821">
-      <c r="T821" s="4"/>
+      <c r="T821" s="5"/>
     </row>
     <row r="822">
-      <c r="T822" s="4"/>
+      <c r="T822" s="5"/>
     </row>
     <row r="823">
-      <c r="T823" s="4"/>
+      <c r="T823" s="5"/>
     </row>
     <row r="824">
-      <c r="T824" s="4"/>
+      <c r="T824" s="5"/>
     </row>
     <row r="825">
-      <c r="T825" s="4"/>
+      <c r="T825" s="5"/>
     </row>
     <row r="826">
-      <c r="T826" s="4"/>
+      <c r="T826" s="5"/>
     </row>
     <row r="827">
-      <c r="T827" s="4"/>
+      <c r="T827" s="5"/>
     </row>
     <row r="828">
-      <c r="T828" s="4"/>
+      <c r="T828" s="5"/>
     </row>
     <row r="829">
-      <c r="T829" s="4"/>
+      <c r="T829" s="5"/>
     </row>
     <row r="830">
-      <c r="T830" s="4"/>
+      <c r="T830" s="5"/>
     </row>
     <row r="831">
-      <c r="T831" s="4"/>
+      <c r="T831" s="5"/>
     </row>
     <row r="832">
-      <c r="T832" s="4"/>
+      <c r="T832" s="5"/>
     </row>
     <row r="833">
-      <c r="T833" s="4"/>
+      <c r="T833" s="5"/>
     </row>
     <row r="834">
-      <c r="T834" s="4"/>
+      <c r="T834" s="5"/>
     </row>
     <row r="835">
-      <c r="T835" s="4"/>
+      <c r="T835" s="5"/>
     </row>
     <row r="836">
-      <c r="T836" s="4"/>
+      <c r="T836" s="5"/>
     </row>
     <row r="837">
-      <c r="T837" s="4"/>
+      <c r="T837" s="5"/>
     </row>
     <row r="838">
-      <c r="T838" s="4"/>
+      <c r="T838" s="5"/>
     </row>
     <row r="839">
-      <c r="T839" s="4"/>
+      <c r="T839" s="5"/>
     </row>
     <row r="840">
-      <c r="T840" s="4"/>
+      <c r="T840" s="5"/>
     </row>
     <row r="841">
-      <c r="T841" s="4"/>
+      <c r="T841" s="5"/>
     </row>
     <row r="842">
-      <c r="T842" s="4"/>
+      <c r="T842" s="5"/>
     </row>
     <row r="843">
-      <c r="T843" s="4"/>
+      <c r="T843" s="5"/>
     </row>
     <row r="844">
-      <c r="T844" s="4"/>
+      <c r="T844" s="5"/>
     </row>
     <row r="845">
-      <c r="T845" s="4"/>
+      <c r="T845" s="5"/>
     </row>
     <row r="846">
-      <c r="T846" s="4"/>
+      <c r="T846" s="5"/>
     </row>
     <row r="847">
-      <c r="T847" s="4"/>
+      <c r="T847" s="5"/>
     </row>
     <row r="848">
-      <c r="T848" s="4"/>
+      <c r="T848" s="5"/>
     </row>
     <row r="849">
-      <c r="T849" s="4"/>
+      <c r="T849" s="5"/>
     </row>
     <row r="850">
-      <c r="T850" s="4"/>
+      <c r="T850" s="5"/>
     </row>
     <row r="851">
-      <c r="T851" s="4"/>
+      <c r="T851" s="5"/>
     </row>
     <row r="852">
-      <c r="T852" s="4"/>
+      <c r="T852" s="5"/>
     </row>
     <row r="853">
-      <c r="T853" s="4"/>
+      <c r="T853" s="5"/>
     </row>
     <row r="854">
-      <c r="T854" s="4"/>
+      <c r="T854" s="5"/>
     </row>
     <row r="855">
-      <c r="T855" s="4"/>
+      <c r="T855" s="5"/>
     </row>
     <row r="856">
-      <c r="T856" s="4"/>
+      <c r="T856" s="5"/>
     </row>
     <row r="857">
-      <c r="T857" s="4"/>
+      <c r="T857" s="5"/>
     </row>
     <row r="858">
-      <c r="T858" s="4"/>
+      <c r="T858" s="5"/>
     </row>
     <row r="859">
-      <c r="T859" s="4"/>
+      <c r="T859" s="5"/>
     </row>
     <row r="860">
-      <c r="T860" s="4"/>
+      <c r="T860" s="5"/>
     </row>
     <row r="861">
-      <c r="T861" s="4"/>
+      <c r="T861" s="5"/>
     </row>
     <row r="862">
-      <c r="T862" s="4"/>
+      <c r="T862" s="5"/>
     </row>
     <row r="863">
-      <c r="T863" s="4"/>
+      <c r="T863" s="5"/>
     </row>
     <row r="864">
-      <c r="T864" s="4"/>
+      <c r="T864" s="5"/>
     </row>
     <row r="865">
-      <c r="T865" s="4"/>
+      <c r="T865" s="5"/>
     </row>
     <row r="866">
-      <c r="T866" s="4"/>
+      <c r="T866" s="5"/>
     </row>
     <row r="867">
-      <c r="T867" s="4"/>
+      <c r="T867" s="5"/>
     </row>
     <row r="868">
-      <c r="T868" s="4"/>
+      <c r="T868" s="5"/>
     </row>
     <row r="869">
-      <c r="T869" s="4"/>
+      <c r="T869" s="5"/>
     </row>
     <row r="870">
-      <c r="T870" s="4"/>
+      <c r="T870" s="5"/>
     </row>
     <row r="871">
-      <c r="T871" s="4"/>
+      <c r="T871" s="5"/>
     </row>
     <row r="872">
-      <c r="T872" s="4"/>
+      <c r="T872" s="5"/>
     </row>
     <row r="873">
-      <c r="T873" s="4"/>
+      <c r="T873" s="5"/>
     </row>
     <row r="874">
-      <c r="T874" s="4"/>
+      <c r="T874" s="5"/>
     </row>
     <row r="875">
-      <c r="T875" s="4"/>
+      <c r="T875" s="5"/>
     </row>
     <row r="876">
-      <c r="T876" s="4"/>
+      <c r="T876" s="5"/>
     </row>
     <row r="877">
-      <c r="T877" s="4"/>
+      <c r="T877" s="5"/>
     </row>
     <row r="878">
-      <c r="T878" s="4"/>
+      <c r="T878" s="5"/>
     </row>
     <row r="879">
-      <c r="T879" s="4"/>
+      <c r="T879" s="5"/>
     </row>
     <row r="880">
-      <c r="T880" s="4"/>
+      <c r="T880" s="5"/>
     </row>
     <row r="881">
-      <c r="T881" s="4"/>
+      <c r="T881" s="5"/>
     </row>
     <row r="882">
-      <c r="T882" s="4"/>
+      <c r="T882" s="5"/>
     </row>
     <row r="883">
-      <c r="T883" s="4"/>
+      <c r="T883" s="5"/>
     </row>
     <row r="884">
-      <c r="T884" s="4"/>
+      <c r="T884" s="5"/>
     </row>
     <row r="885">
-      <c r="T885" s="4"/>
+      <c r="T885" s="5"/>
     </row>
     <row r="886">
-      <c r="T886" s="4"/>
+      <c r="T886" s="5"/>
     </row>
     <row r="887">
-      <c r="T887" s="4"/>
+      <c r="T887" s="5"/>
     </row>
     <row r="888">
-      <c r="T888" s="4"/>
+      <c r="T888" s="5"/>
     </row>
     <row r="889">
-      <c r="T889" s="4"/>
+      <c r="T889" s="5"/>
     </row>
     <row r="890">
-      <c r="T890" s="4"/>
+      <c r="T890" s="5"/>
     </row>
     <row r="891">
-      <c r="T891" s="4"/>
+      <c r="T891" s="5"/>
     </row>
     <row r="892">
-      <c r="T892" s="4"/>
+      <c r="T892" s="5"/>
     </row>
     <row r="893">
-      <c r="T893" s="4"/>
+      <c r="T893" s="5"/>
     </row>
     <row r="894">
-      <c r="T894" s="4"/>
+      <c r="T894" s="5"/>
     </row>
     <row r="895">
-      <c r="T895" s="4"/>
+      <c r="T895" s="5"/>
     </row>
     <row r="896">
-      <c r="T896" s="4"/>
+      <c r="T896" s="5"/>
     </row>
     <row r="897">
-      <c r="T897" s="4"/>
+      <c r="T897" s="5"/>
     </row>
     <row r="898">
-      <c r="T898" s="4"/>
+      <c r="T898" s="5"/>
     </row>
     <row r="899">
-      <c r="T899" s="4"/>
+      <c r="T899" s="5"/>
     </row>
     <row r="900">
-      <c r="T900" s="4"/>
+      <c r="T900" s="5"/>
     </row>
     <row r="901">
-      <c r="T901" s="4"/>
+      <c r="T901" s="5"/>
     </row>
     <row r="902">
-      <c r="T902" s="4"/>
+      <c r="T902" s="5"/>
     </row>
     <row r="903">
-      <c r="T903" s="4"/>
+      <c r="T903" s="5"/>
     </row>
     <row r="904">
-      <c r="T904" s="4"/>
+      <c r="T904" s="5"/>
     </row>
     <row r="905">
-      <c r="T905" s="4"/>
+      <c r="T905" s="5"/>
     </row>
     <row r="906">
-      <c r="T906" s="4"/>
+      <c r="T906" s="5"/>
     </row>
     <row r="907">
-      <c r="T907" s="4"/>
+      <c r="T907" s="5"/>
     </row>
     <row r="908">
-      <c r="T908" s="4"/>
+      <c r="T908" s="5"/>
     </row>
     <row r="909">
-      <c r="T909" s="4"/>
+      <c r="T909" s="5"/>
     </row>
     <row r="910">
-      <c r="T910" s="4"/>
+      <c r="T910" s="5"/>
     </row>
     <row r="911">
-      <c r="T911" s="4"/>
+      <c r="T911" s="5"/>
     </row>
     <row r="912">
-      <c r="T912" s="4"/>
+      <c r="T912" s="5"/>
     </row>
     <row r="913">
-      <c r="T913" s="4"/>
+      <c r="T913" s="5"/>
     </row>
     <row r="914">
-      <c r="T914" s="4"/>
+      <c r="T914" s="5"/>
     </row>
     <row r="915">
-      <c r="T915" s="4"/>
+      <c r="T915" s="5"/>
     </row>
     <row r="916">
-      <c r="T916" s="4"/>
+      <c r="T916" s="5"/>
     </row>
     <row r="917">
-      <c r="T917" s="4"/>
+      <c r="T917" s="5"/>
     </row>
     <row r="918">
-      <c r="T918" s="4"/>
+      <c r="T918" s="5"/>
     </row>
     <row r="919">
-      <c r="T919" s="4"/>
+      <c r="T919" s="5"/>
     </row>
     <row r="920">
-      <c r="T920" s="4"/>
+      <c r="T920" s="5"/>
     </row>
     <row r="921">
-      <c r="T921" s="4"/>
+      <c r="T921" s="5"/>
     </row>
     <row r="922">
-      <c r="T922" s="4"/>
+      <c r="T922" s="5"/>
     </row>
     <row r="923">
-      <c r="T923" s="4"/>
+      <c r="T923" s="5"/>
     </row>
     <row r="924">
-      <c r="T924" s="4"/>
+      <c r="T924" s="5"/>
     </row>
     <row r="925">
-      <c r="T925" s="4"/>
+      <c r="T925" s="5"/>
     </row>
     <row r="926">
-      <c r="T926" s="4"/>
+      <c r="T926" s="5"/>
     </row>
     <row r="927">
-      <c r="T927" s="4"/>
+      <c r="T927" s="5"/>
     </row>
     <row r="928">
-      <c r="T928" s="4"/>
+      <c r="T928" s="5"/>
     </row>
     <row r="929">
-      <c r="T929" s="4"/>
+      <c r="T929" s="5"/>
     </row>
     <row r="930">
-      <c r="T930" s="4"/>
+      <c r="T930" s="5"/>
     </row>
     <row r="931">
-      <c r="T931" s="4"/>
+      <c r="T931" s="5"/>
     </row>
     <row r="932">
-      <c r="T932" s="4"/>
+      <c r="T932" s="5"/>
     </row>
     <row r="933">
-      <c r="T933" s="4"/>
+      <c r="T933" s="5"/>
     </row>
     <row r="934">
-      <c r="T934" s="4"/>
+      <c r="T934" s="5"/>
     </row>
     <row r="935">
-      <c r="T935" s="4"/>
+      <c r="T935" s="5"/>
     </row>
     <row r="936">
-      <c r="T936" s="4"/>
+      <c r="T936" s="5"/>
     </row>
     <row r="937">
-      <c r="T937" s="4"/>
+      <c r="T937" s="5"/>
     </row>
     <row r="938">
-      <c r="T938" s="4"/>
+      <c r="T938" s="5"/>
     </row>
     <row r="939">
-      <c r="T939" s="4"/>
+      <c r="T939" s="5"/>
     </row>
     <row r="940">
-      <c r="T940" s="4"/>
+      <c r="T940" s="5"/>
     </row>
     <row r="941">
-      <c r="T941" s="4"/>
+      <c r="T941" s="5"/>
     </row>
     <row r="942">
-      <c r="T942" s="4"/>
+      <c r="T942" s="5"/>
     </row>
     <row r="943">
-      <c r="T943" s="4"/>
+      <c r="T943" s="5"/>
     </row>
     <row r="944">
-      <c r="T944" s="4"/>
+      <c r="T944" s="5"/>
     </row>
     <row r="945">
-      <c r="T945" s="4"/>
+      <c r="T945" s="5"/>
     </row>
     <row r="946">
-      <c r="T946" s="4"/>
+      <c r="T946" s="5"/>
     </row>
     <row r="947">
-      <c r="T947" s="4"/>
+      <c r="T947" s="5"/>
     </row>
     <row r="948">
-      <c r="T948" s="4"/>
+      <c r="T948" s="5"/>
     </row>
     <row r="949">
-      <c r="T949" s="4"/>
+      <c r="T949" s="5"/>
     </row>
     <row r="950">
-      <c r="T950" s="4"/>
+      <c r="T950" s="5"/>
     </row>
     <row r="951">
-      <c r="T951" s="4"/>
+      <c r="T951" s="5"/>
     </row>
     <row r="952">
-      <c r="T952" s="4"/>
+      <c r="T952" s="5"/>
     </row>
     <row r="953">
-      <c r="T953" s="4"/>
+      <c r="T953" s="5"/>
     </row>
     <row r="954">
-      <c r="T954" s="4"/>
+      <c r="T954" s="5"/>
     </row>
     <row r="955">
-      <c r="T955" s="4"/>
+      <c r="T955" s="5"/>
     </row>
     <row r="956">
-      <c r="T956" s="4"/>
+      <c r="T956" s="5"/>
     </row>
     <row r="957">
-      <c r="T957" s="4"/>
+      <c r="T957" s="5"/>
     </row>
     <row r="958">
-      <c r="T958" s="4"/>
+      <c r="T958" s="5"/>
     </row>
     <row r="959">
-      <c r="T959" s="4"/>
+      <c r="T959" s="5"/>
     </row>
     <row r="960">
-      <c r="T960" s="4"/>
+      <c r="T960" s="5"/>
     </row>
     <row r="961">
-      <c r="T961" s="4"/>
+      <c r="T961" s="5"/>
     </row>
     <row r="962">
-      <c r="T962" s="4"/>
+      <c r="T962" s="5"/>
     </row>
     <row r="963">
-      <c r="T963" s="4"/>
+      <c r="T963" s="5"/>
     </row>
     <row r="964">
-      <c r="T964" s="4"/>
+      <c r="T964" s="5"/>
     </row>
     <row r="965">
-      <c r="T965" s="4"/>
+      <c r="T965" s="5"/>
     </row>
     <row r="966">
-      <c r="T966" s="4"/>
+      <c r="T966" s="5"/>
     </row>
     <row r="967">
-      <c r="T967" s="4"/>
+      <c r="T967" s="5"/>
     </row>
     <row r="968">
-      <c r="T968" s="4"/>
+      <c r="T968" s="5"/>
     </row>
     <row r="969">
-      <c r="T969" s="4"/>
+      <c r="T969" s="5"/>
     </row>
     <row r="970">
-      <c r="T970" s="4"/>
+      <c r="T970" s="5"/>
     </row>
     <row r="971">
-      <c r="T971" s="4"/>
+      <c r="T971" s="5"/>
     </row>
     <row r="972">
-      <c r="T972" s="4"/>
+      <c r="T972" s="5"/>
     </row>
     <row r="973">
-      <c r="T973" s="4"/>
+      <c r="T973" s="5"/>
     </row>
     <row r="974">
-      <c r="T974" s="4"/>
+      <c r="T974" s="5"/>
     </row>
     <row r="975">
-      <c r="T975" s="4"/>
+      <c r="T975" s="5"/>
     </row>
     <row r="976">
-      <c r="T976" s="4"/>
+      <c r="T976" s="5"/>
     </row>
     <row r="977">
-      <c r="T977" s="4"/>
+      <c r="T977" s="5"/>
     </row>
     <row r="978">
-      <c r="T978" s="4"/>
+      <c r="T978" s="5"/>
     </row>
     <row r="979">
-      <c r="T979" s="4"/>
+      <c r="T979" s="5"/>
     </row>
     <row r="980">
-      <c r="T980" s="4"/>
+      <c r="T980" s="5"/>
     </row>
     <row r="981">
-      <c r="T981" s="4"/>
+      <c r="T981" s="5"/>
     </row>
     <row r="982">
-      <c r="T982" s="4"/>
+      <c r="T982" s="5"/>
     </row>
     <row r="983">
-      <c r="T983" s="4"/>
+      <c r="T983" s="5"/>
     </row>
     <row r="984">
-      <c r="T984" s="4"/>
+      <c r="T984" s="5"/>
     </row>
     <row r="985">
-      <c r="T985" s="4"/>
+      <c r="T985" s="5"/>
     </row>
     <row r="986">
-      <c r="T986" s="4"/>
+      <c r="T986" s="5"/>
     </row>
     <row r="987">
-      <c r="T987" s="4"/>
+      <c r="T987" s="5"/>
     </row>
     <row r="988">
-      <c r="T988" s="4"/>
+      <c r="T988" s="5"/>
     </row>
     <row r="989">
-      <c r="T989" s="4"/>
+      <c r="T989" s="5"/>
     </row>
     <row r="990">
-      <c r="T990" s="4"/>
+      <c r="T990" s="5"/>
     </row>
     <row r="991">
-      <c r="T991" s="4"/>
+      <c r="T991" s="5"/>
     </row>
     <row r="992">
-      <c r="T992" s="4"/>
+      <c r="T992" s="5"/>
     </row>
     <row r="993">
-      <c r="T993" s="4"/>
+      <c r="T993" s="5"/>
     </row>
     <row r="994">
-      <c r="T994" s="4"/>
+      <c r="T994" s="5"/>
     </row>
     <row r="995">
-      <c r="T995" s="4"/>
+      <c r="T995" s="5"/>
     </row>
     <row r="996">
-      <c r="T996" s="4"/>
+      <c r="T996" s="5"/>
     </row>
     <row r="997">
-      <c r="T997" s="4"/>
+      <c r="T997" s="5"/>
     </row>
     <row r="998">
-      <c r="T998" s="4"/>
+      <c r="T998" s="5"/>
     </row>
     <row r="999">
-      <c r="T999" s="4"/>
+      <c r="T999" s="5"/>
     </row>
     <row r="1000">
-      <c r="T1000" s="4"/>
+      <c r="T1000" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$U$1000"/>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M67">
+      <formula1>"Dempeus,Diversa,Estirat,Suspès,Dempeus inclinat,Assegut/estirat,Planxa,Lateral,Assegut,Dempeus o assegut,Inclinat,Invertida/inclinada,Assegut elevat,Dempeus/terra,Estirat lateral,Quadrupèdia"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T2:T1000">
       <formula1>"Sí,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N67">
+      <formula1>"Bilateral,Altern,Unilateral,Unilateral/altern"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O67">
+      <formula1>"Inicial,Intermedi,Avançat"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
